--- a/Python/tests/vte/data/Fiche de coûts V6.1 - TEL.xlsx
+++ b/Python/tests/vte/data/Fiche de coûts V6.1 - TEL.xlsx
@@ -1,38 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\FORMATIONS_C\TEL\P05-P06-dossier-conception-referentiel\fiche-de-cout-et-code-de-formation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83BCB12-1043-47A0-BCD3-810EA7D59530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E331B7-4D2B-4B1C-A567-4E5DACC3AB21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1050" yWindow="-120" windowWidth="27870" windowHeight="16440" tabRatio="731" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="731" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gestion des versions" sheetId="19" r:id="rId1"/>
     <sheet name="Mode d'emploi" sheetId="15" r:id="rId2"/>
     <sheet name="Table FD&amp;FC" sheetId="18" r:id="rId3"/>
     <sheet name="Fiche de coûts" sheetId="1" r:id="rId4"/>
-    <sheet name="LMS" sheetId="16" r:id="rId5"/>
-    <sheet name="Conception numérique" sheetId="17" r:id="rId6"/>
-    <sheet name="Coûts installations" sheetId="2" r:id="rId7"/>
-    <sheet name="Coûts frais variables" sheetId="3" r:id="rId8"/>
-    <sheet name="Coûts frais déplacement" sheetId="4" r:id="rId9"/>
+    <sheet name="Feuil1" sheetId="20" r:id="rId5"/>
+    <sheet name="LMS" sheetId="16" r:id="rId6"/>
+    <sheet name="Conception numérique" sheetId="17" r:id="rId7"/>
+    <sheet name="Coûts installations" sheetId="2" r:id="rId8"/>
+    <sheet name="Coûts frais variables" sheetId="3" r:id="rId9"/>
+    <sheet name="Coûts frais déplacement" sheetId="4" r:id="rId10"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId11"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Table FD&amp;FC'!$U$3:$W$98</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Table FD&amp;FC'!$3:$3</definedName>
     <definedName name="marge">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Conception numérique'!$A$1:$C$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Conception numérique'!$A$1:$C$37</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Fiche de coûts'!$A$1:$N$104</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">LMS!$A$1:$D$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">LMS!$A$1:$D$23</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Table FD&amp;FC'!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -45,6 +50,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -129,7 +137,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Vincent TESTARD:</t>
         </r>
@@ -138,7 +146,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 7,25 h de cours et 11h30 de TP à 2 intervenants</t>
@@ -201,6 +209,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Vincent TESTARD:</t>
         </r>
@@ -209,6 +218,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Accès au télémanipulateur : 500 €/pers.
@@ -221,7 +231,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="714">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1452" uniqueCount="744">
   <si>
     <t>Poste de dépenses</t>
   </si>
@@ -2888,12 +2898,102 @@
   <si>
     <t>Réingénierie continue</t>
   </si>
+  <si>
+    <t>€/pers.</t>
+  </si>
+  <si>
+    <t>somme(K87-&gt;K95) pour T1 ou pareil avec L si on veut T3</t>
+  </si>
+  <si>
+    <t>Dans onglet frais variables</t>
+  </si>
+  <si>
+    <t>Ecart lié aux repas (où il y a un +2 pour les accompagants) -&gt; Valeur négligeable sur l'ensemble → Mettre 0 €/personne voire en part fixe au besoin</t>
+  </si>
+  <si>
+    <t>Calcul man</t>
+  </si>
+  <si>
+    <t>Nouvell val</t>
+  </si>
+  <si>
+    <t>Val FdC</t>
+  </si>
+  <si>
+    <t>Coût part variable par personne</t>
+  </si>
+  <si>
+    <t>Coût fixe conception</t>
+  </si>
+  <si>
+    <t>Coût fixe réalisation</t>
+  </si>
+  <si>
+    <t>€</t>
+  </si>
+  <si>
+    <t>Calcul avec Coût complet CEA (L)</t>
+  </si>
+  <si>
+    <t>Ecart minime lié aux repas (où il y a un +2 pour les accompagants) -&gt; Valeur négligeable sur l'ensemble → Mettre 0 €/personne voire en part fixe au besoin</t>
+  </si>
+  <si>
+    <t>Ici exclu pour la tel</t>
+  </si>
+  <si>
+    <t>L56</t>
+  </si>
+  <si>
+    <t>somme(L64 → L86 ; L96→L103) ou L9-L56</t>
+  </si>
+  <si>
+    <t>somme(L87-&gt;L95) pour T3 ou L10/C17</t>
+  </si>
+  <si>
+    <t>Coût fixe total</t>
+  </si>
+  <si>
+    <t>Somme 2 sous-calculs</t>
+  </si>
+  <si>
+    <t>Nb_participants_Min</t>
+  </si>
+  <si>
+    <t>Prix fixé T3</t>
+  </si>
+  <si>
+    <t>J22</t>
+  </si>
+  <si>
+    <t>Prix_fixé_par_personne [€/pes.] = Coûts_fixes [€]/nb_participants_Min [pers.] + coût_part_variable [€/pers.]</t>
+  </si>
+  <si>
+    <t>Prix_fixé_par_personne [€/pes.] - coût_part_variable [€/pers.] = Coûts_fixes [€]/nb_participants_Min [pers.]</t>
+  </si>
+  <si>
+    <t>(Prix_fixé_par_personne [€/pes.] - coût_part_variable [€/pers.])/Coûts_fixes [€] = 1/nb_participants_Min [pers.]</t>
+  </si>
+  <si>
+    <t>nb_participants_Min [pers.] = Coûts_fixes [€] / (Prix_fixé_par_personne [€/pes.] - coût_part_variable [€/pers.])</t>
+  </si>
+  <si>
+    <t>nb participants cible</t>
+  </si>
+  <si>
+    <t>Montant hors aléas</t>
+  </si>
+  <si>
+    <t>dont part fixe</t>
+  </si>
+  <si>
+    <t>dont part variable</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="10">
+  <numFmts count="13">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="0.000000"/>
@@ -2904,8 +3004,11 @@
     <numFmt numFmtId="171" formatCode="0&quot; €/pers&quot;"/>
     <numFmt numFmtId="172" formatCode="_-* #,##0\ &quot;€&quot;_-;\-* #,##0\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
     <numFmt numFmtId="173" formatCode="0&quot; €/pers.&quot;"/>
+    <numFmt numFmtId="174" formatCode="#,##0&quot; €&quot;"/>
+    <numFmt numFmtId="175" formatCode="#,##0&quot; €/p.&quot;"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0\ [$€-40C]_-;\-* #,##0\ [$€-40C]_-;_-* &quot;-&quot;??\ [$€-40C]_-;_-@_-"/>
   </numFmts>
-  <fonts count="48" x14ac:knownFonts="1">
+  <fonts count="45" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3243,31 +3346,14 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3406,6 +3492,11 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="109">
     <border>
@@ -4798,12 +4889,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="876">
+  <cellXfs count="885">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -6605,6 +6697,28 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="84" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="174" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="175" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="174" fontId="44" fillId="24" borderId="0" xfId="3" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -7315,25 +7429,15 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="84" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
+    <cellStyle name="Neutre" xfId="3" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
@@ -8200,6 +8304,46 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Gestion des versions"/>
+      <sheetName val="Mode d'emploi"/>
+      <sheetName val="Table FD&amp;FC"/>
+      <sheetName val="Fiche de coûts"/>
+      <sheetName val="LMS"/>
+      <sheetName val="Conception numérique"/>
+      <sheetName val="Coûts installations"/>
+      <sheetName val="Coûts frais variables"/>
+      <sheetName val="Coûts frais déplacement"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="8">
+          <cell r="L8">
+            <v>7871</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="C17">
+            <v>6</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
@@ -8628,6 +8772,527 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <sheetPr>
+    <tabColor theme="8" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:J48"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="35.85546875" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" customWidth="1"/>
+    <col min="9" max="9" width="16.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="65" t="s">
+        <v>110</v>
+      </c>
+      <c r="B2" s="65"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="65"/>
+      <c r="B3" s="65"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="65"/>
+      <c r="B4" s="65"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="65"/>
+      <c r="B5" s="65"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="65"/>
+      <c r="B6" s="65"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="65"/>
+      <c r="B7" s="65"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="65"/>
+      <c r="B8" s="65"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="65"/>
+      <c r="B9" s="65"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="65"/>
+      <c r="B10" s="65"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="65"/>
+      <c r="B11" s="65"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="65"/>
+      <c r="B12" s="65"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="65"/>
+      <c r="B13" s="65"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="65"/>
+      <c r="B14" s="65"/>
+    </row>
+    <row r="15" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:9" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="874" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16" s="875"/>
+      <c r="E16" s="874" t="s">
+        <v>111</v>
+      </c>
+      <c r="F16" s="876"/>
+      <c r="G16" s="874" t="s">
+        <v>141</v>
+      </c>
+      <c r="H16" s="876"/>
+      <c r="I16" s="872" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="67" t="s">
+        <v>113</v>
+      </c>
+      <c r="B17" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="72" t="s">
+        <v>257</v>
+      </c>
+      <c r="D17" s="73" t="s">
+        <v>85</v>
+      </c>
+      <c r="E17" s="72" t="s">
+        <v>257</v>
+      </c>
+      <c r="F17" s="73" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17" s="72" t="s">
+        <v>257</v>
+      </c>
+      <c r="H17" s="73" t="s">
+        <v>85</v>
+      </c>
+      <c r="I17" s="873"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="66" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" s="616"/>
+      <c r="D18" s="536"/>
+      <c r="E18" s="616"/>
+      <c r="F18" s="536"/>
+      <c r="G18" s="616"/>
+      <c r="H18" s="536"/>
+      <c r="I18" s="71">
+        <f t="shared" ref="I18:I25" si="0">C18*D18+E18*F18+G18*H18</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="588" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="66" t="s">
+        <v>349</v>
+      </c>
+      <c r="B19" s="36" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" s="539"/>
+      <c r="D19" s="536"/>
+      <c r="E19" s="539"/>
+      <c r="F19" s="536"/>
+      <c r="G19" s="539"/>
+      <c r="H19" s="536"/>
+      <c r="I19" s="69">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="66" t="s">
+        <v>350</v>
+      </c>
+      <c r="B20" s="36" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" s="539"/>
+      <c r="D20" s="536"/>
+      <c r="E20" s="539"/>
+      <c r="F20" s="536"/>
+      <c r="G20" s="539"/>
+      <c r="H20" s="536"/>
+      <c r="I20" s="69">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="66" t="s">
+        <v>351</v>
+      </c>
+      <c r="B21" s="36" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="539"/>
+      <c r="D21" s="536"/>
+      <c r="E21" s="539"/>
+      <c r="F21" s="536"/>
+      <c r="G21" s="539"/>
+      <c r="H21" s="536"/>
+      <c r="I21" s="69">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="B22" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" s="614">
+        <v>130</v>
+      </c>
+      <c r="D22" s="615"/>
+      <c r="E22" s="614">
+        <v>110</v>
+      </c>
+      <c r="F22" s="537"/>
+      <c r="G22" s="539"/>
+      <c r="H22" s="537"/>
+      <c r="I22" s="69">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="B23" s="36" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" s="614">
+        <v>22</v>
+      </c>
+      <c r="D23" s="615"/>
+      <c r="E23" s="614">
+        <v>22</v>
+      </c>
+      <c r="F23" s="537"/>
+      <c r="G23" s="539"/>
+      <c r="H23" s="537"/>
+      <c r="I23" s="69">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="B24" s="36" t="s">
+        <v>108</v>
+      </c>
+      <c r="C24" s="614">
+        <v>20.2</v>
+      </c>
+      <c r="D24" s="615"/>
+      <c r="E24" s="614">
+        <v>20.2</v>
+      </c>
+      <c r="F24" s="537"/>
+      <c r="G24" s="539"/>
+      <c r="H24" s="537"/>
+      <c r="I24" s="69">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="631" t="s">
+        <v>700</v>
+      </c>
+      <c r="B25" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="C25" s="612"/>
+      <c r="D25" s="538"/>
+      <c r="E25" s="612"/>
+      <c r="F25" s="538"/>
+      <c r="G25" s="612"/>
+      <c r="H25" s="538"/>
+      <c r="I25" s="70">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I26" s="74">
+        <f>SUM(I18:I25)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I27" s="375"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="65" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="266" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="1:9" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="B37" s="879" t="s">
+        <v>573</v>
+      </c>
+      <c r="C37" s="880"/>
+      <c r="D37" s="880"/>
+      <c r="E37" s="880"/>
+      <c r="F37" s="880"/>
+      <c r="G37" s="880"/>
+      <c r="H37" s="881"/>
+      <c r="I37" s="591"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="467"/>
+      <c r="B38" s="592"/>
+      <c r="C38" s="467"/>
+      <c r="D38" s="467"/>
+      <c r="E38" s="467"/>
+      <c r="F38" s="467"/>
+      <c r="G38" s="467"/>
+      <c r="H38" s="593"/>
+      <c r="I38" s="467"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="467"/>
+      <c r="B39" s="864" t="s">
+        <v>562</v>
+      </c>
+      <c r="C39" s="865"/>
+      <c r="D39" s="477"/>
+      <c r="E39" s="468"/>
+      <c r="F39" s="469"/>
+      <c r="G39" s="469"/>
+      <c r="H39" s="594"/>
+      <c r="I39" s="467"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="467"/>
+      <c r="B40" s="592"/>
+      <c r="C40" s="467"/>
+      <c r="D40" s="467"/>
+      <c r="E40" s="467"/>
+      <c r="F40" s="467"/>
+      <c r="G40" s="467"/>
+      <c r="H40" s="593"/>
+      <c r="I40" s="467"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="467"/>
+      <c r="B41" s="595"/>
+      <c r="C41" s="470"/>
+      <c r="D41" s="866" t="s">
+        <v>563</v>
+      </c>
+      <c r="E41" s="866"/>
+      <c r="F41" s="866"/>
+      <c r="G41" s="866"/>
+      <c r="H41" s="867"/>
+      <c r="I41" s="467"/>
+    </row>
+    <row r="42" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A42" s="589"/>
+      <c r="B42" s="868" t="s">
+        <v>564</v>
+      </c>
+      <c r="C42" s="869"/>
+      <c r="D42" s="471" t="s">
+        <v>565</v>
+      </c>
+      <c r="E42" s="587" t="s">
+        <v>566</v>
+      </c>
+      <c r="F42" s="471" t="s">
+        <v>567</v>
+      </c>
+      <c r="G42" s="587" t="s">
+        <v>568</v>
+      </c>
+      <c r="H42" s="596" t="s">
+        <v>569</v>
+      </c>
+      <c r="I42" s="589"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="467"/>
+      <c r="B43" s="877" t="s">
+        <v>570</v>
+      </c>
+      <c r="C43" s="878"/>
+      <c r="D43" s="473">
+        <v>0.32</v>
+      </c>
+      <c r="E43" s="473">
+        <v>0.35</v>
+      </c>
+      <c r="F43" s="473">
+        <v>0.37</v>
+      </c>
+      <c r="G43" s="473">
+        <v>0.08</v>
+      </c>
+      <c r="H43" s="597">
+        <v>0.12</v>
+      </c>
+      <c r="I43" s="467"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="467"/>
+      <c r="B44" s="598" t="s">
+        <v>571</v>
+      </c>
+      <c r="C44" s="472"/>
+      <c r="D44" s="473">
+        <v>0.15</v>
+      </c>
+      <c r="E44" s="473">
+        <v>0.17</v>
+      </c>
+      <c r="F44" s="473">
+        <v>0.18</v>
+      </c>
+      <c r="G44" s="473">
+        <v>0.08</v>
+      </c>
+      <c r="H44" s="597">
+        <v>0.12</v>
+      </c>
+      <c r="I44" s="467"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="467"/>
+      <c r="B45" s="595"/>
+      <c r="C45" s="470"/>
+      <c r="D45" s="470"/>
+      <c r="E45" s="470"/>
+      <c r="F45" s="470"/>
+      <c r="G45" s="470"/>
+      <c r="H45" s="599"/>
+      <c r="I45" s="467"/>
+    </row>
+    <row r="46" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A46" s="467"/>
+      <c r="B46" s="595"/>
+      <c r="C46" s="470"/>
+      <c r="D46" s="474" t="s">
+        <v>565</v>
+      </c>
+      <c r="E46" s="475" t="s">
+        <v>566</v>
+      </c>
+      <c r="F46" s="474" t="s">
+        <v>567</v>
+      </c>
+      <c r="G46" s="587" t="s">
+        <v>568</v>
+      </c>
+      <c r="H46" s="600" t="s">
+        <v>569</v>
+      </c>
+      <c r="I46" s="467"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="590"/>
+      <c r="B47" s="870" t="s">
+        <v>572</v>
+      </c>
+      <c r="C47" s="871"/>
+      <c r="D47" s="476">
+        <f>IF(D39&lt;1000,(D39*D43),(D39*D44))</f>
+        <v>0</v>
+      </c>
+      <c r="E47" s="476">
+        <f>IF(D39&lt;1000,(D39*E43),(D39*E44))</f>
+        <v>0</v>
+      </c>
+      <c r="F47" s="476">
+        <f>IF(D39&lt;1000,(D39*F43),(D39*F44))</f>
+        <v>0</v>
+      </c>
+      <c r="G47" s="476">
+        <f>IF(D39&lt;1000,(D39*G43),(D39*G44))</f>
+        <v>0</v>
+      </c>
+      <c r="H47" s="601">
+        <f>IF(D39&lt;1000,(D39*H43),(D39*H44))</f>
+        <v>0</v>
+      </c>
+      <c r="I47" s="590"/>
+    </row>
+    <row r="48" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="467"/>
+      <c r="B48" s="602"/>
+      <c r="C48" s="603"/>
+      <c r="D48" s="603"/>
+      <c r="E48" s="603"/>
+      <c r="F48" s="603"/>
+      <c r="G48" s="603"/>
+      <c r="H48" s="604"/>
+      <c r="I48" s="467"/>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1" scenarios="1"/>
+  <mergeCells count="10">
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B37:H37"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A30" r:id="rId1" xr:uid="{00000000-0004-0000-0800-000000000000}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId2"/>
+  <drawing r:id="rId3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
@@ -8802,10 +9467,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A1" s="650" t="s">
+      <c r="A1" s="660" t="s">
         <v>502</v>
       </c>
-      <c r="B1" s="650"/>
+      <c r="B1" s="660"/>
     </row>
     <row r="2" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8843,10 +9508,10 @@
       </c>
     </row>
     <row r="4" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="654" t="s">
+      <c r="A4" s="664" t="s">
         <v>425</v>
       </c>
-      <c r="B4" s="651" t="s">
+      <c r="B4" s="661" t="s">
         <v>426</v>
       </c>
       <c r="C4" s="206" t="s">
@@ -8886,8 +9551,8 @@
       </c>
     </row>
     <row r="5" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="654"/>
-      <c r="B5" s="652"/>
+      <c r="A5" s="664"/>
+      <c r="B5" s="662"/>
       <c r="C5" s="190" t="s">
         <v>211</v>
       </c>
@@ -8925,8 +9590,8 @@
       </c>
     </row>
     <row r="6" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="654"/>
-      <c r="B6" s="652"/>
+      <c r="A6" s="664"/>
+      <c r="B6" s="662"/>
       <c r="C6" s="191" t="s">
         <v>214</v>
       </c>
@@ -8964,8 +9629,8 @@
       </c>
     </row>
     <row r="7" spans="1:23" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="654"/>
-      <c r="B7" s="653"/>
+      <c r="A7" s="664"/>
+      <c r="B7" s="663"/>
       <c r="C7" s="199" t="s">
         <v>212</v>
       </c>
@@ -9003,8 +9668,8 @@
       </c>
     </row>
     <row r="8" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="654"/>
-      <c r="B8" s="656" t="s">
+      <c r="A8" s="664"/>
+      <c r="B8" s="666" t="s">
         <v>427</v>
       </c>
       <c r="C8" s="206" t="s">
@@ -9044,8 +9709,8 @@
       </c>
     </row>
     <row r="9" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="654"/>
-      <c r="B9" s="657"/>
+      <c r="A9" s="664"/>
+      <c r="B9" s="667"/>
       <c r="C9" s="190" t="s">
         <v>451</v>
       </c>
@@ -9083,8 +9748,8 @@
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A10" s="654"/>
-      <c r="B10" s="657"/>
+      <c r="A10" s="664"/>
+      <c r="B10" s="667"/>
       <c r="C10" s="191" t="s">
         <v>170</v>
       </c>
@@ -9122,8 +9787,8 @@
       </c>
     </row>
     <row r="11" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="654"/>
-      <c r="B11" s="658"/>
+      <c r="A11" s="664"/>
+      <c r="B11" s="668"/>
       <c r="C11" s="199" t="s">
         <v>172</v>
       </c>
@@ -9161,8 +9826,8 @@
       </c>
     </row>
     <row r="12" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="654"/>
-      <c r="B12" s="656" t="s">
+      <c r="A12" s="664"/>
+      <c r="B12" s="666" t="s">
         <v>428</v>
       </c>
       <c r="C12" s="206" t="s">
@@ -9202,8 +9867,8 @@
       </c>
     </row>
     <row r="13" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="654"/>
-      <c r="B13" s="657"/>
+      <c r="A13" s="664"/>
+      <c r="B13" s="667"/>
       <c r="C13" s="190" t="s">
         <v>186</v>
       </c>
@@ -9241,8 +9906,8 @@
       </c>
     </row>
     <row r="14" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="654"/>
-      <c r="B14" s="658"/>
+      <c r="A14" s="664"/>
+      <c r="B14" s="668"/>
       <c r="C14" s="199" t="s">
         <v>187</v>
       </c>
@@ -9280,8 +9945,8 @@
       </c>
     </row>
     <row r="15" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="654"/>
-      <c r="B15" s="656" t="s">
+      <c r="A15" s="664"/>
+      <c r="B15" s="666" t="s">
         <v>429</v>
       </c>
       <c r="C15" s="206" t="s">
@@ -9321,8 +9986,8 @@
       </c>
     </row>
     <row r="16" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="654"/>
-      <c r="B16" s="657"/>
+      <c r="A16" s="664"/>
+      <c r="B16" s="667"/>
       <c r="C16" s="192" t="s">
         <v>454</v>
       </c>
@@ -9360,8 +10025,8 @@
       </c>
     </row>
     <row r="17" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="654"/>
-      <c r="B17" s="657"/>
+      <c r="A17" s="664"/>
+      <c r="B17" s="667"/>
       <c r="C17" s="191" t="s">
         <v>191</v>
       </c>
@@ -9399,8 +10064,8 @@
       </c>
     </row>
     <row r="18" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="654"/>
-      <c r="B18" s="657"/>
+      <c r="A18" s="664"/>
+      <c r="B18" s="667"/>
       <c r="C18" s="191" t="s">
         <v>430</v>
       </c>
@@ -9438,8 +10103,8 @@
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A19" s="654"/>
-      <c r="B19" s="657"/>
+      <c r="A19" s="664"/>
+      <c r="B19" s="667"/>
       <c r="C19" s="191" t="s">
         <v>189</v>
       </c>
@@ -9477,8 +10142,8 @@
       </c>
     </row>
     <row r="20" spans="1:23" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="654"/>
-      <c r="B20" s="658"/>
+      <c r="A20" s="664"/>
+      <c r="B20" s="668"/>
       <c r="C20" s="199" t="s">
         <v>192</v>
       </c>
@@ -9516,8 +10181,8 @@
       </c>
     </row>
     <row r="21" spans="1:23" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="654"/>
-      <c r="B21" s="656" t="s">
+      <c r="A21" s="664"/>
+      <c r="B21" s="666" t="s">
         <v>431</v>
       </c>
       <c r="C21" s="206" t="s">
@@ -9557,8 +10222,8 @@
       </c>
     </row>
     <row r="22" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="654"/>
-      <c r="B22" s="657"/>
+      <c r="A22" s="664"/>
+      <c r="B22" s="667"/>
       <c r="C22" s="190" t="s">
         <v>507</v>
       </c>
@@ -9596,8 +10261,8 @@
       </c>
     </row>
     <row r="23" spans="1:23" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="654"/>
-      <c r="B23" s="657"/>
+      <c r="A23" s="664"/>
+      <c r="B23" s="667"/>
       <c r="C23" s="190" t="s">
         <v>456</v>
       </c>
@@ -9635,8 +10300,8 @@
       </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A24" s="654"/>
-      <c r="B24" s="657"/>
+      <c r="A24" s="664"/>
+      <c r="B24" s="667"/>
       <c r="C24" s="190" t="s">
         <v>178</v>
       </c>
@@ -9674,8 +10339,8 @@
       </c>
     </row>
     <row r="25" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="654"/>
-      <c r="B25" s="658"/>
+      <c r="A25" s="664"/>
+      <c r="B25" s="668"/>
       <c r="C25" s="199" t="s">
         <v>176</v>
       </c>
@@ -9713,8 +10378,8 @@
       </c>
     </row>
     <row r="26" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="654"/>
-      <c r="B26" s="656" t="s">
+      <c r="A26" s="664"/>
+      <c r="B26" s="666" t="s">
         <v>432</v>
       </c>
       <c r="C26" s="206" t="s">
@@ -9754,8 +10419,8 @@
       </c>
     </row>
     <row r="27" spans="1:23" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="654"/>
-      <c r="B27" s="657"/>
+      <c r="A27" s="664"/>
+      <c r="B27" s="667"/>
       <c r="C27" s="190" t="s">
         <v>459</v>
       </c>
@@ -9793,8 +10458,8 @@
       </c>
     </row>
     <row r="28" spans="1:23" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="654"/>
-      <c r="B28" s="657"/>
+      <c r="A28" s="664"/>
+      <c r="B28" s="667"/>
       <c r="C28" s="190" t="s">
         <v>182</v>
       </c>
@@ -9832,8 +10497,8 @@
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A29" s="654"/>
-      <c r="B29" s="657"/>
+      <c r="A29" s="664"/>
+      <c r="B29" s="667"/>
       <c r="C29" s="192" t="s">
         <v>461</v>
       </c>
@@ -9871,8 +10536,8 @@
       </c>
     </row>
     <row r="30" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="654"/>
-      <c r="B30" s="657"/>
+      <c r="A30" s="664"/>
+      <c r="B30" s="667"/>
       <c r="C30" s="191" t="s">
         <v>183</v>
       </c>
@@ -9910,8 +10575,8 @@
       </c>
     </row>
     <row r="31" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="654"/>
-      <c r="B31" s="657"/>
+      <c r="A31" s="664"/>
+      <c r="B31" s="667"/>
       <c r="C31" s="191" t="s">
         <v>180</v>
       </c>
@@ -9949,8 +10614,8 @@
       </c>
     </row>
     <row r="32" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="654"/>
-      <c r="B32" s="658"/>
+      <c r="A32" s="664"/>
+      <c r="B32" s="668"/>
       <c r="C32" s="199" t="s">
         <v>181</v>
       </c>
@@ -9988,8 +10653,8 @@
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A33" s="654"/>
-      <c r="B33" s="659" t="s">
+      <c r="A33" s="664"/>
+      <c r="B33" s="669" t="s">
         <v>433</v>
       </c>
       <c r="C33" s="198" t="s">
@@ -10029,8 +10694,8 @@
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A34" s="654"/>
-      <c r="B34" s="660"/>
+      <c r="A34" s="664"/>
+      <c r="B34" s="670"/>
       <c r="C34" s="191" t="s">
         <v>174</v>
       </c>
@@ -10068,8 +10733,8 @@
       </c>
     </row>
     <row r="35" spans="1:23" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="654"/>
-      <c r="B35" s="661"/>
+      <c r="A35" s="664"/>
+      <c r="B35" s="671"/>
       <c r="C35" s="199" t="s">
         <v>173</v>
       </c>
@@ -10107,7 +10772,7 @@
       </c>
     </row>
     <row r="36" spans="1:23" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="654"/>
+      <c r="A36" s="664"/>
       <c r="B36" s="207" t="s">
         <v>434</v>
       </c>
@@ -10148,8 +10813,8 @@
       </c>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A37" s="654"/>
-      <c r="B37" s="662" t="s">
+      <c r="A37" s="664"/>
+      <c r="B37" s="672" t="s">
         <v>464</v>
       </c>
       <c r="C37" s="209" t="s">
@@ -10189,8 +10854,8 @@
       </c>
     </row>
     <row r="38" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="655"/>
-      <c r="B38" s="663"/>
+      <c r="A38" s="665"/>
+      <c r="B38" s="673"/>
       <c r="C38" s="205" t="s">
         <v>199</v>
       </c>
@@ -10228,10 +10893,10 @@
       </c>
     </row>
     <row r="39" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="641" t="s">
+      <c r="A39" s="651" t="s">
         <v>435</v>
       </c>
-      <c r="B39" s="644" t="s">
+      <c r="B39" s="654" t="s">
         <v>436</v>
       </c>
       <c r="C39" s="194" t="s">
@@ -10271,8 +10936,8 @@
       </c>
     </row>
     <row r="40" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="642"/>
-      <c r="B40" s="645"/>
+      <c r="A40" s="652"/>
+      <c r="B40" s="655"/>
       <c r="C40" s="188" t="s">
         <v>202</v>
       </c>
@@ -10310,8 +10975,8 @@
       </c>
     </row>
     <row r="41" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="642"/>
-      <c r="B41" s="645"/>
+      <c r="A41" s="652"/>
+      <c r="B41" s="655"/>
       <c r="C41" s="188" t="s">
         <v>207</v>
       </c>
@@ -10349,8 +11014,8 @@
       </c>
     </row>
     <row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="642"/>
-      <c r="B42" s="645"/>
+      <c r="A42" s="652"/>
+      <c r="B42" s="655"/>
       <c r="C42" s="188" t="s">
         <v>208</v>
       </c>
@@ -10388,8 +11053,8 @@
       </c>
     </row>
     <row r="43" spans="1:23" ht="30" x14ac:dyDescent="0.25">
-      <c r="A43" s="642"/>
-      <c r="B43" s="645"/>
+      <c r="A43" s="652"/>
+      <c r="B43" s="655"/>
       <c r="C43" s="188" t="s">
         <v>203</v>
       </c>
@@ -10427,8 +11092,8 @@
       </c>
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A44" s="642"/>
-      <c r="B44" s="645"/>
+      <c r="A44" s="652"/>
+      <c r="B44" s="655"/>
       <c r="C44" s="188" t="s">
         <v>204</v>
       </c>
@@ -10466,8 +11131,8 @@
       </c>
     </row>
     <row r="45" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="642"/>
-      <c r="B45" s="645"/>
+      <c r="A45" s="652"/>
+      <c r="B45" s="655"/>
       <c r="C45" s="189" t="s">
         <v>205</v>
       </c>
@@ -10505,8 +11170,8 @@
       </c>
     </row>
     <row r="46" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="642"/>
-      <c r="B46" s="645"/>
+      <c r="A46" s="652"/>
+      <c r="B46" s="655"/>
       <c r="C46" s="189" t="s">
         <v>200</v>
       </c>
@@ -10544,8 +11209,8 @@
       </c>
     </row>
     <row r="47" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="642"/>
-      <c r="B47" s="645"/>
+      <c r="A47" s="652"/>
+      <c r="B47" s="655"/>
       <c r="C47" s="189" t="s">
         <v>206</v>
       </c>
@@ -10583,8 +11248,8 @@
       </c>
     </row>
     <row r="48" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="643"/>
-      <c r="B48" s="646"/>
+      <c r="A48" s="653"/>
+      <c r="B48" s="656"/>
       <c r="C48" s="195" t="s">
         <v>209</v>
       </c>
@@ -10622,10 +11287,10 @@
       </c>
     </row>
     <row r="49" spans="1:23" ht="30" x14ac:dyDescent="0.25">
-      <c r="A49" s="647" t="s">
+      <c r="A49" s="657" t="s">
         <v>437</v>
       </c>
-      <c r="B49" s="667" t="s">
+      <c r="B49" s="677" t="s">
         <v>438</v>
       </c>
       <c r="C49" s="196" t="s">
@@ -10665,8 +11330,8 @@
       </c>
     </row>
     <row r="50" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A50" s="648"/>
-      <c r="B50" s="668"/>
+      <c r="A50" s="658"/>
+      <c r="B50" s="678"/>
       <c r="C50" s="186" t="s">
         <v>235</v>
       </c>
@@ -10704,8 +11369,8 @@
       </c>
     </row>
     <row r="51" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="648"/>
-      <c r="B51" s="668"/>
+      <c r="A51" s="658"/>
+      <c r="B51" s="678"/>
       <c r="C51" s="186" t="s">
         <v>236</v>
       </c>
@@ -10743,8 +11408,8 @@
       </c>
     </row>
     <row r="52" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="648"/>
-      <c r="B52" s="668"/>
+      <c r="A52" s="658"/>
+      <c r="B52" s="678"/>
       <c r="C52" s="186" t="s">
         <v>228</v>
       </c>
@@ -10782,8 +11447,8 @@
       </c>
     </row>
     <row r="53" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="648"/>
-      <c r="B53" s="668"/>
+      <c r="A53" s="658"/>
+      <c r="B53" s="678"/>
       <c r="C53" s="186" t="s">
         <v>237</v>
       </c>
@@ -10821,8 +11486,8 @@
       </c>
     </row>
     <row r="54" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="648"/>
-      <c r="B54" s="668"/>
+      <c r="A54" s="658"/>
+      <c r="B54" s="678"/>
       <c r="C54" s="187" t="s">
         <v>239</v>
       </c>
@@ -10860,8 +11525,8 @@
       </c>
     </row>
     <row r="55" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="648"/>
-      <c r="B55" s="668"/>
+      <c r="A55" s="658"/>
+      <c r="B55" s="678"/>
       <c r="C55" s="187" t="s">
         <v>238</v>
       </c>
@@ -10899,8 +11564,8 @@
       </c>
     </row>
     <row r="56" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="648"/>
-      <c r="B56" s="668"/>
+      <c r="A56" s="658"/>
+      <c r="B56" s="678"/>
       <c r="C56" s="187" t="s">
         <v>233</v>
       </c>
@@ -10938,8 +11603,8 @@
       </c>
     </row>
     <row r="57" spans="1:23" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="649"/>
-      <c r="B57" s="669"/>
+      <c r="A57" s="659"/>
+      <c r="B57" s="679"/>
       <c r="C57" s="197" t="s">
         <v>232</v>
       </c>
@@ -10977,10 +11642,10 @@
       </c>
     </row>
     <row r="58" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="670" t="s">
+      <c r="A58" s="680" t="s">
         <v>439</v>
       </c>
-      <c r="B58" s="672" t="s">
+      <c r="B58" s="682" t="s">
         <v>440</v>
       </c>
       <c r="C58" s="200" t="s">
@@ -11020,8 +11685,8 @@
       </c>
     </row>
     <row r="59" spans="1:23" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="671"/>
-      <c r="B59" s="673"/>
+      <c r="A59" s="681"/>
+      <c r="B59" s="683"/>
       <c r="C59" s="201" t="s">
         <v>231</v>
       </c>
@@ -11059,8 +11724,8 @@
       </c>
     </row>
     <row r="60" spans="1:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="671"/>
-      <c r="B60" s="674" t="s">
+      <c r="A60" s="681"/>
+      <c r="B60" s="684" t="s">
         <v>441</v>
       </c>
       <c r="C60" s="210" t="s">
@@ -11100,8 +11765,8 @@
       </c>
     </row>
     <row r="61" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A61" s="671"/>
-      <c r="B61" s="675"/>
+      <c r="A61" s="681"/>
+      <c r="B61" s="685"/>
       <c r="C61" s="193" t="s">
         <v>224</v>
       </c>
@@ -11139,8 +11804,8 @@
       </c>
     </row>
     <row r="62" spans="1:23" ht="30" x14ac:dyDescent="0.25">
-      <c r="A62" s="671"/>
-      <c r="B62" s="675"/>
+      <c r="A62" s="681"/>
+      <c r="B62" s="685"/>
       <c r="C62" s="193" t="s">
         <v>227</v>
       </c>
@@ -11178,8 +11843,8 @@
       </c>
     </row>
     <row r="63" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A63" s="671"/>
-      <c r="B63" s="675"/>
+      <c r="A63" s="681"/>
+      <c r="B63" s="685"/>
       <c r="C63" s="193" t="s">
         <v>225</v>
       </c>
@@ -11217,8 +11882,8 @@
       </c>
     </row>
     <row r="64" spans="1:23" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="671"/>
-      <c r="B64" s="675"/>
+      <c r="A64" s="681"/>
+      <c r="B64" s="685"/>
       <c r="C64" s="193" t="s">
         <v>229</v>
       </c>
@@ -11256,10 +11921,10 @@
       </c>
     </row>
     <row r="65" spans="1:23" ht="45" x14ac:dyDescent="0.25">
-      <c r="A65" s="682" t="s">
+      <c r="A65" s="692" t="s">
         <v>442</v>
       </c>
-      <c r="B65" s="685" t="s">
+      <c r="B65" s="695" t="s">
         <v>443</v>
       </c>
       <c r="C65" s="202" t="s">
@@ -11299,8 +11964,8 @@
       </c>
     </row>
     <row r="66" spans="1:23" ht="30" x14ac:dyDescent="0.25">
-      <c r="A66" s="683"/>
-      <c r="B66" s="686"/>
+      <c r="A66" s="693"/>
+      <c r="B66" s="696"/>
       <c r="C66" s="184" t="s">
         <v>616</v>
       </c>
@@ -11338,8 +12003,8 @@
       </c>
     </row>
     <row r="67" spans="1:23" ht="30" x14ac:dyDescent="0.25">
-      <c r="A67" s="683"/>
-      <c r="B67" s="686"/>
+      <c r="A67" s="693"/>
+      <c r="B67" s="696"/>
       <c r="C67" s="184" t="s">
         <v>682</v>
       </c>
@@ -11377,8 +12042,8 @@
       </c>
     </row>
     <row r="68" spans="1:23" ht="30" x14ac:dyDescent="0.25">
-      <c r="A68" s="683"/>
-      <c r="B68" s="686"/>
+      <c r="A68" s="693"/>
+      <c r="B68" s="696"/>
       <c r="C68" s="184" t="s">
         <v>217</v>
       </c>
@@ -11416,8 +12081,8 @@
       </c>
     </row>
     <row r="69" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A69" s="683"/>
-      <c r="B69" s="686"/>
+      <c r="A69" s="693"/>
+      <c r="B69" s="696"/>
       <c r="C69" s="184" t="s">
         <v>463</v>
       </c>
@@ -11455,8 +12120,8 @@
       </c>
     </row>
     <row r="70" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A70" s="683"/>
-      <c r="B70" s="686"/>
+      <c r="A70" s="693"/>
+      <c r="B70" s="696"/>
       <c r="C70" s="184" t="s">
         <v>623</v>
       </c>
@@ -11474,7 +12139,7 @@
       <c r="K70" s="359"/>
       <c r="L70" s="359"/>
       <c r="Q70" t="str">
-        <f t="shared" ref="Q70:Q71" si="2">D70</f>
+        <f>D70</f>
         <v>LOCFORMDLSMX</v>
       </c>
       <c r="R70" t="s">
@@ -11494,8 +12159,8 @@
       </c>
     </row>
     <row r="71" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A71" s="683"/>
-      <c r="B71" s="686"/>
+      <c r="A71" s="693"/>
+      <c r="B71" s="696"/>
       <c r="C71" s="184" t="s">
         <v>684</v>
       </c>
@@ -11513,7 +12178,7 @@
       <c r="K71" s="359"/>
       <c r="L71" s="359"/>
       <c r="Q71" t="str">
-        <f t="shared" si="2"/>
+        <f>D71</f>
         <v>LOCFORMDM2RX</v>
       </c>
       <c r="R71" t="s">
@@ -11533,8 +12198,8 @@
       </c>
     </row>
     <row r="72" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A72" s="683"/>
-      <c r="B72" s="686"/>
+      <c r="A72" s="693"/>
+      <c r="B72" s="696"/>
       <c r="C72" s="185" t="s">
         <v>218</v>
       </c>
@@ -11572,8 +12237,8 @@
       </c>
     </row>
     <row r="73" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A73" s="683"/>
-      <c r="B73" s="686"/>
+      <c r="A73" s="693"/>
+      <c r="B73" s="696"/>
       <c r="C73" s="185" t="s">
         <v>221</v>
       </c>
@@ -11611,8 +12276,8 @@
       </c>
     </row>
     <row r="74" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A74" s="683"/>
-      <c r="B74" s="686"/>
+      <c r="A74" s="693"/>
+      <c r="B74" s="696"/>
       <c r="C74" s="185" t="s">
         <v>215</v>
       </c>
@@ -11650,8 +12315,8 @@
       </c>
     </row>
     <row r="75" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A75" s="683"/>
-      <c r="B75" s="686"/>
+      <c r="A75" s="693"/>
+      <c r="B75" s="696"/>
       <c r="C75" s="185" t="s">
         <v>220</v>
       </c>
@@ -11689,8 +12354,8 @@
       </c>
     </row>
     <row r="76" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="683"/>
-      <c r="B76" s="686"/>
+      <c r="A76" s="693"/>
+      <c r="B76" s="696"/>
       <c r="C76" s="185" t="s">
         <v>219</v>
       </c>
@@ -11728,8 +12393,8 @@
       </c>
     </row>
     <row r="77" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="683"/>
-      <c r="B77" s="687"/>
+      <c r="A77" s="693"/>
+      <c r="B77" s="697"/>
       <c r="C77" s="584" t="s">
         <v>680</v>
       </c>
@@ -11767,8 +12432,8 @@
       </c>
     </row>
     <row r="78" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="683"/>
-      <c r="B78" s="688"/>
+      <c r="A78" s="693"/>
+      <c r="B78" s="698"/>
       <c r="C78" s="203" t="s">
         <v>222</v>
       </c>
@@ -11806,8 +12471,8 @@
       </c>
     </row>
     <row r="79" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A79" s="683"/>
-      <c r="B79" s="685" t="s">
+      <c r="A79" s="693"/>
+      <c r="B79" s="695" t="s">
         <v>444</v>
       </c>
       <c r="C79" s="213" t="s">
@@ -11847,8 +12512,8 @@
       </c>
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A80" s="683"/>
-      <c r="B80" s="686"/>
+      <c r="A80" s="693"/>
+      <c r="B80" s="696"/>
       <c r="C80" s="185" t="s">
         <v>196</v>
       </c>
@@ -11886,8 +12551,8 @@
       </c>
     </row>
     <row r="81" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A81" s="683"/>
-      <c r="B81" s="686"/>
+      <c r="A81" s="693"/>
+      <c r="B81" s="696"/>
       <c r="C81" s="185" t="s">
         <v>194</v>
       </c>
@@ -11925,8 +12590,8 @@
       </c>
     </row>
     <row r="82" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="683"/>
-      <c r="B82" s="686"/>
+      <c r="A82" s="693"/>
+      <c r="B82" s="696"/>
       <c r="C82" s="185" t="s">
         <v>445</v>
       </c>
@@ -11964,8 +12629,8 @@
       </c>
     </row>
     <row r="83" spans="1:23" s="177" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="683"/>
-      <c r="B83" s="688"/>
+      <c r="A83" s="693"/>
+      <c r="B83" s="698"/>
       <c r="C83" s="203" t="s">
         <v>226</v>
       </c>
@@ -12007,8 +12672,8 @@
       </c>
     </row>
     <row r="84" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="683"/>
-      <c r="B84" s="685" t="s">
+      <c r="A84" s="693"/>
+      <c r="B84" s="695" t="s">
         <v>446</v>
       </c>
       <c r="C84" s="202" t="s">
@@ -12048,8 +12713,8 @@
       </c>
     </row>
     <row r="85" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A85" s="683"/>
-      <c r="B85" s="686"/>
+      <c r="A85" s="693"/>
+      <c r="B85" s="696"/>
       <c r="C85" s="185" t="s">
         <v>184</v>
       </c>
@@ -12087,8 +12752,8 @@
       </c>
     </row>
     <row r="86" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A86" s="683"/>
-      <c r="B86" s="686"/>
+      <c r="A86" s="693"/>
+      <c r="B86" s="696"/>
       <c r="C86" s="185" t="s">
         <v>188</v>
       </c>
@@ -12126,8 +12791,8 @@
       </c>
     </row>
     <row r="87" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="683"/>
-      <c r="B87" s="686"/>
+      <c r="A87" s="693"/>
+      <c r="B87" s="696"/>
       <c r="C87" s="185" t="s">
         <v>193</v>
       </c>
@@ -12165,8 +12830,8 @@
       </c>
     </row>
     <row r="88" spans="1:23" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="684"/>
-      <c r="B88" s="688"/>
+      <c r="A88" s="694"/>
+      <c r="B88" s="698"/>
       <c r="C88" s="203" t="s">
         <v>179</v>
       </c>
@@ -12204,7 +12869,7 @@
       </c>
     </row>
     <row r="89" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="676" t="s">
+      <c r="A89" s="686" t="s">
         <v>508</v>
       </c>
       <c r="B89" s="340" t="s">
@@ -12247,8 +12912,8 @@
       </c>
     </row>
     <row r="90" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A90" s="677"/>
-      <c r="B90" s="679" t="s">
+      <c r="A90" s="687"/>
+      <c r="B90" s="689" t="s">
         <v>550</v>
       </c>
       <c r="C90" s="341" t="s">
@@ -12288,8 +12953,8 @@
       </c>
     </row>
     <row r="91" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A91" s="677"/>
-      <c r="B91" s="680"/>
+      <c r="A91" s="687"/>
+      <c r="B91" s="690"/>
       <c r="C91" s="344" t="s">
         <v>551</v>
       </c>
@@ -12327,8 +12992,8 @@
       </c>
     </row>
     <row r="92" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="677"/>
-      <c r="B92" s="680"/>
+      <c r="A92" s="687"/>
+      <c r="B92" s="690"/>
       <c r="C92" s="344" t="s">
         <v>379</v>
       </c>
@@ -12366,8 +13031,8 @@
       </c>
     </row>
     <row r="93" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="677"/>
-      <c r="B93" s="680"/>
+      <c r="A93" s="687"/>
+      <c r="B93" s="690"/>
       <c r="C93" s="344" t="s">
         <v>554</v>
       </c>
@@ -12405,8 +13070,8 @@
       </c>
     </row>
     <row r="94" spans="1:23" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="678"/>
-      <c r="B94" s="681"/>
+      <c r="A94" s="688"/>
+      <c r="B94" s="691"/>
       <c r="C94" s="347" t="s">
         <v>556</v>
       </c>
@@ -12444,7 +13109,7 @@
       </c>
     </row>
     <row r="95" spans="1:23" ht="30" x14ac:dyDescent="0.25">
-      <c r="A95" s="664" t="s">
+      <c r="A95" s="674" t="s">
         <v>447</v>
       </c>
       <c r="B95" s="350" t="s">
@@ -12487,7 +13152,7 @@
       </c>
     </row>
     <row r="96" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="665"/>
+      <c r="A96" s="675"/>
       <c r="B96" s="353" t="s">
         <v>449</v>
       </c>
@@ -12528,7 +13193,7 @@
       </c>
     </row>
     <row r="97" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="666"/>
+      <c r="A97" s="676"/>
       <c r="B97" s="356" t="s">
         <v>464</v>
       </c>
@@ -12652,40 +13317,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="740" t="s">
+      <c r="A1" s="750" t="s">
         <v>706</v>
       </c>
-      <c r="B1" s="740"/>
-      <c r="C1" s="740"/>
-      <c r="D1" s="740"/>
-      <c r="E1" s="740"/>
-      <c r="F1" s="740"/>
-      <c r="G1" s="740"/>
-      <c r="H1" s="740"/>
-      <c r="I1" s="740"/>
-      <c r="J1" s="740"/>
-      <c r="K1" s="740"/>
-      <c r="L1" s="740"/>
-      <c r="M1" s="740"/>
-      <c r="N1" s="740"/>
+      <c r="B1" s="750"/>
+      <c r="C1" s="750"/>
+      <c r="D1" s="750"/>
+      <c r="E1" s="750"/>
+      <c r="F1" s="750"/>
+      <c r="G1" s="750"/>
+      <c r="H1" s="750"/>
+      <c r="I1" s="750"/>
+      <c r="J1" s="750"/>
+      <c r="K1" s="750"/>
+      <c r="L1" s="750"/>
+      <c r="M1" s="750"/>
+      <c r="N1" s="750"/>
     </row>
     <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="781" t="s">
+      <c r="A2" s="791" t="s">
         <v>629</v>
       </c>
-      <c r="B2" s="781"/>
-      <c r="C2" s="781"/>
-      <c r="D2" s="781"/>
-      <c r="E2" s="781"/>
-      <c r="F2" s="781"/>
-      <c r="G2" s="781"/>
-      <c r="H2" s="781"/>
-      <c r="I2" s="781"/>
-      <c r="J2" s="781"/>
-      <c r="K2" s="781"/>
-      <c r="L2" s="781"/>
-      <c r="M2" s="781"/>
-      <c r="N2" s="781"/>
+      <c r="B2" s="791"/>
+      <c r="C2" s="791"/>
+      <c r="D2" s="791"/>
+      <c r="E2" s="791"/>
+      <c r="F2" s="791"/>
+      <c r="G2" s="791"/>
+      <c r="H2" s="791"/>
+      <c r="I2" s="791"/>
+      <c r="J2" s="791"/>
+      <c r="K2" s="791"/>
+      <c r="L2" s="791"/>
+      <c r="M2" s="791"/>
+      <c r="N2" s="791"/>
       <c r="O2" s="93"/>
     </row>
     <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12710,12 +13375,12 @@
       <c r="B5" s="101" t="s">
         <v>144</v>
       </c>
-      <c r="C5" s="795" t="s">
+      <c r="C5" s="805" t="s">
         <v>707</v>
       </c>
-      <c r="D5" s="796"/>
-      <c r="E5" s="796"/>
-      <c r="F5" s="797"/>
+      <c r="D5" s="806"/>
+      <c r="E5" s="806"/>
+      <c r="F5" s="807"/>
       <c r="J5" s="376" t="s">
         <v>635</v>
       </c>
@@ -12734,23 +13399,23 @@
       </c>
     </row>
     <row r="6" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="782" t="s">
+      <c r="B6" s="792" t="s">
         <v>691</v>
       </c>
-      <c r="C6" s="784">
+      <c r="C6" s="794">
         <f>IF(I57=0,1,I57)</f>
         <v>1</v>
       </c>
-      <c r="D6" s="711" t="s">
+      <c r="D6" s="721" t="s">
         <v>692</v>
       </c>
-      <c r="E6" s="712"/>
-      <c r="F6" s="712"/>
-      <c r="G6" s="701" t="s">
+      <c r="E6" s="722"/>
+      <c r="F6" s="722"/>
+      <c r="G6" s="711" t="s">
         <v>528</v>
       </c>
-      <c r="H6" s="702"/>
-      <c r="I6" s="702"/>
+      <c r="H6" s="712"/>
+      <c r="I6" s="712"/>
       <c r="J6" s="568">
         <f>J13*C20</f>
         <v>10884</v>
@@ -12768,21 +13433,21 @@
         <f>N13*C20</f>
         <v>12612</v>
       </c>
-      <c r="O6" s="699" t="s">
+      <c r="O6" s="709" t="s">
         <v>535</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="783"/>
-      <c r="C7" s="785"/>
-      <c r="D7" s="713"/>
-      <c r="E7" s="714"/>
-      <c r="F7" s="714"/>
-      <c r="G7" s="706" t="s">
+      <c r="B7" s="793"/>
+      <c r="C7" s="795"/>
+      <c r="D7" s="723"/>
+      <c r="E7" s="724"/>
+      <c r="F7" s="724"/>
+      <c r="G7" s="716" t="s">
         <v>529</v>
       </c>
-      <c r="H7" s="707"/>
-      <c r="I7" s="708"/>
+      <c r="H7" s="717"/>
+      <c r="I7" s="718"/>
       <c r="J7" s="570">
         <f>J6-J12*C21</f>
         <v>0</v>
@@ -12800,7 +13465,7 @@
         <f>N6-J12*C21</f>
         <v>1728</v>
       </c>
-      <c r="O7" s="700"/>
+      <c r="O7" s="710"/>
     </row>
     <row r="8" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="80" t="s">
@@ -12809,20 +13474,20 @@
       <c r="C8" s="379" t="s">
         <v>708</v>
       </c>
-      <c r="D8" s="715"/>
-      <c r="E8" s="716"/>
-      <c r="F8" s="716"/>
-      <c r="G8" s="717" t="s">
+      <c r="D8" s="725"/>
+      <c r="E8" s="726"/>
+      <c r="F8" s="726"/>
+      <c r="G8" s="727" t="s">
         <v>530</v>
       </c>
-      <c r="H8" s="718"/>
-      <c r="I8" s="719"/>
+      <c r="H8" s="728"/>
+      <c r="I8" s="729"/>
       <c r="J8" s="572">
         <f>J12-J11</f>
         <v>4947</v>
       </c>
       <c r="K8" s="572">
-        <f t="shared" ref="K8:M8" si="0">K12-K11</f>
+        <f>K12-K11</f>
         <v>7080</v>
       </c>
       <c r="L8" s="572">
@@ -12830,14 +13495,14 @@
         <v>7871</v>
       </c>
       <c r="M8" s="572">
-        <f t="shared" si="0"/>
+        <f>M12-M11</f>
         <v>8656</v>
       </c>
       <c r="N8" s="572">
         <f>N12-N11</f>
         <v>6306</v>
       </c>
-      <c r="O8" s="699" t="s">
+      <c r="O8" s="709" t="s">
         <v>536</v>
       </c>
     </row>
@@ -12848,46 +13513,46 @@
       <c r="C9" s="380">
         <v>1999</v>
       </c>
-      <c r="G9" s="801" t="s">
+      <c r="G9" s="811" t="s">
         <v>133</v>
       </c>
-      <c r="H9" s="802"/>
-      <c r="I9" s="803"/>
+      <c r="H9" s="812"/>
+      <c r="I9" s="813"/>
       <c r="J9" s="573">
         <f>J8-J10</f>
         <v>3221.94</v>
       </c>
       <c r="K9" s="573">
-        <f t="shared" ref="K9:M9" si="1">K8-K10</f>
+        <f>K8-K10</f>
         <v>5478</v>
       </c>
       <c r="L9" s="573">
-        <f t="shared" si="1"/>
+        <f>L8-L10</f>
         <v>6090.7380800000001</v>
       </c>
       <c r="M9" s="573">
-        <f t="shared" si="1"/>
+        <f>M8-M10</f>
         <v>6697.7118879999998</v>
       </c>
       <c r="N9" s="573">
         <f>N8-N10</f>
         <v>4080.6725999999999</v>
       </c>
-      <c r="O9" s="720"/>
+      <c r="O9" s="730"/>
     </row>
     <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="C10" s="709" t="s">
+      <c r="C10" s="719" t="s">
         <v>709</v>
       </c>
-      <c r="D10" s="710"/>
-      <c r="G10" s="801" t="s">
+      <c r="D10" s="720"/>
+      <c r="G10" s="811" t="s">
         <v>132</v>
       </c>
-      <c r="H10" s="802"/>
-      <c r="I10" s="803"/>
+      <c r="H10" s="812"/>
+      <c r="I10" s="813"/>
       <c r="J10" s="573">
         <f>K87+K88+K89+K90+K91+K92+K93+K94+K95</f>
         <v>1725.06</v>
@@ -12908,7 +13573,7 @@
         <f>N87+N88+N89+N90+N91+N92+N93+N94+N95</f>
         <v>2225.3274000000001</v>
       </c>
-      <c r="O10" s="720"/>
+      <c r="O10" s="730"/>
     </row>
     <row r="11" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5" t="s">
@@ -12917,45 +13582,45 @@
       <c r="C11" s="381">
         <v>3</v>
       </c>
-      <c r="G11" s="807" t="s">
+      <c r="G11" s="817" t="s">
         <v>602</v>
       </c>
-      <c r="H11" s="808"/>
-      <c r="I11" s="809"/>
+      <c r="H11" s="818"/>
+      <c r="I11" s="819"/>
       <c r="J11" s="583">
         <f>ROUND(J12-J12/1.1,0)</f>
         <v>495</v>
       </c>
       <c r="K11" s="583">
-        <f t="shared" ref="K11:M11" si="2">ROUND(K12-K12/1.1,0)</f>
+        <f>ROUND(K12-K12/1.1,0)</f>
         <v>708</v>
       </c>
       <c r="L11" s="583">
-        <f t="shared" si="2"/>
+        <f>ROUND(L12-L12/1.1,0)</f>
         <v>787</v>
       </c>
       <c r="M11" s="583">
-        <f t="shared" si="2"/>
+        <f>ROUND(M12-M12/1.1,0)</f>
         <v>866</v>
       </c>
       <c r="N11" s="618">
         <v>0</v>
       </c>
-      <c r="O11" s="720"/>
+      <c r="O11" s="730"/>
     </row>
     <row r="12" spans="1:16" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C12" s="697" t="s">
+      <c r="C12" s="707" t="s">
         <v>710</v>
       </c>
-      <c r="D12" s="698"/>
-      <c r="G12" s="804" t="s">
+      <c r="D12" s="708"/>
+      <c r="G12" s="814" t="s">
         <v>531</v>
       </c>
-      <c r="H12" s="805"/>
-      <c r="I12" s="806"/>
+      <c r="H12" s="815"/>
+      <c r="I12" s="816"/>
       <c r="J12" s="624">
         <f>ROUND(K35*1.1/C17,0)*C17</f>
         <v>5442</v>
@@ -12976,7 +13641,7 @@
         <f>ROUND(N35/C17,0)*C17</f>
         <v>6306</v>
       </c>
-      <c r="O12" s="721"/>
+      <c r="O12" s="731"/>
       <c r="P12" s="626" t="s">
         <v>694</v>
       </c>
@@ -12985,16 +13650,16 @@
       <c r="B13" s="103" t="s">
         <v>423</v>
       </c>
-      <c r="C13" s="765" t="s">
+      <c r="C13" s="775" t="s">
         <v>272</v>
       </c>
-      <c r="D13" s="766"/>
-      <c r="E13" s="767"/>
-      <c r="G13" s="810" t="s">
+      <c r="D13" s="776"/>
+      <c r="E13" s="777"/>
+      <c r="G13" s="820" t="s">
         <v>532</v>
       </c>
-      <c r="H13" s="811"/>
-      <c r="I13" s="812"/>
+      <c r="H13" s="821"/>
+      <c r="I13" s="822"/>
       <c r="J13" s="619">
         <f>ROUND(J12/C17,0)</f>
         <v>907</v>
@@ -13015,7 +13680,7 @@
         <f>ROUND(N12/C17,0)</f>
         <v>1051</v>
       </c>
-      <c r="O13" s="720"/>
+      <c r="O13" s="730"/>
     </row>
     <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="143" t="s">
@@ -13025,15 +13690,15 @@
         <f>IF(C13="Si OS spécifique : à saisir en D16","Aucun",VLOOKUP(C13,'Table FD&amp;FC'!U4:V98,2,FALSE))</f>
         <v>PROG01</v>
       </c>
-      <c r="D14" s="764" t="s">
+      <c r="D14" s="774" t="s">
         <v>243</v>
       </c>
-      <c r="E14" s="764"/>
-      <c r="G14" s="703" t="s">
+      <c r="E14" s="774"/>
+      <c r="G14" s="713" t="s">
         <v>533</v>
       </c>
-      <c r="H14" s="704"/>
-      <c r="I14" s="705"/>
+      <c r="H14" s="714"/>
+      <c r="I14" s="715"/>
       <c r="J14" s="580">
         <f>IF(OR(LEFT(C10,2)="FC",LEFT(C10,2)="Ce"),ROUND(J12/C11,0),"Non applicable")</f>
         <v>1814</v>
@@ -13054,7 +13719,7 @@
         <f>IF(OR(LEFT(C10,2)="FC",LEFT(C10,2)="Ce"),ROUND(N12/C11,0),"Non applicable")</f>
         <v>2102</v>
       </c>
-      <c r="O14" s="720"/>
+      <c r="O14" s="730"/>
     </row>
     <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="143" t="s">
@@ -13066,11 +13731,11 @@
       </c>
       <c r="D15" s="283"/>
       <c r="E15" s="284"/>
-      <c r="G15" s="703" t="s">
+      <c r="G15" s="713" t="s">
         <v>534</v>
       </c>
-      <c r="H15" s="704"/>
-      <c r="I15" s="705"/>
+      <c r="H15" s="714"/>
+      <c r="I15" s="715"/>
       <c r="J15" s="581">
         <f>IF(LEFT(J14,1)="N",J14,ROUND(J14/C17,0))</f>
         <v>302</v>
@@ -13091,7 +13756,7 @@
         <f>IF(LEFT(N14,1)="N",N14,ROUND(N14/C17,0))</f>
         <v>350</v>
       </c>
-      <c r="O15" s="720"/>
+      <c r="O15" s="730"/>
     </row>
     <row r="16" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="102" t="s">
@@ -13100,16 +13765,16 @@
       <c r="C16" s="382" t="s">
         <v>711</v>
       </c>
-      <c r="D16" s="786" t="s">
+      <c r="D16" s="796" t="s">
         <v>588</v>
       </c>
-      <c r="E16" s="787"/>
-      <c r="F16" s="787"/>
-      <c r="G16" s="798" t="s">
+      <c r="E16" s="797"/>
+      <c r="F16" s="797"/>
+      <c r="G16" s="808" t="s">
         <v>693</v>
       </c>
-      <c r="H16" s="799"/>
-      <c r="I16" s="800"/>
+      <c r="H16" s="809"/>
+      <c r="I16" s="810"/>
       <c r="J16" s="582">
         <f>ROUNDUP(J9/(J13-J10/C17),0)</f>
         <v>6</v>
@@ -13130,7 +13795,7 @@
         <f>ROUNDUP(J9/(N13-J10/C17),0)</f>
         <v>5</v>
       </c>
-      <c r="O16" s="720"/>
+      <c r="O16" s="730"/>
     </row>
     <row r="17" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="101" t="s">
@@ -13142,11 +13807,11 @@
       <c r="D17" s="78"/>
       <c r="E17" s="78"/>
       <c r="F17" s="78"/>
-      <c r="G17" s="703" t="s">
+      <c r="G17" s="713" t="s">
         <v>134</v>
       </c>
-      <c r="H17" s="704"/>
-      <c r="I17" s="705"/>
+      <c r="H17" s="714"/>
+      <c r="I17" s="715"/>
       <c r="J17" s="574">
         <f>J13*J16</f>
         <v>5442</v>
@@ -13167,7 +13832,7 @@
         <f>N13*N16</f>
         <v>5255</v>
       </c>
-      <c r="O17" s="720"/>
+      <c r="O17" s="730"/>
     </row>
     <row r="18" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="101" t="s">
@@ -13179,11 +13844,11 @@
       <c r="D18" s="78"/>
       <c r="E18" s="78"/>
       <c r="F18" s="78"/>
-      <c r="G18" s="706" t="s">
+      <c r="G18" s="716" t="s">
         <v>135</v>
       </c>
-      <c r="H18" s="707"/>
-      <c r="I18" s="708"/>
+      <c r="H18" s="717"/>
+      <c r="I18" s="718"/>
       <c r="J18" s="570">
         <f>ROUND(J9+J10/C17*J16,0)</f>
         <v>4947</v>
@@ -13204,7 +13869,7 @@
         <f>ROUND(J9+J10/C17*N16,0)</f>
         <v>4659</v>
       </c>
-      <c r="O18" s="700"/>
+      <c r="O18" s="710"/>
     </row>
     <row r="19" spans="1:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="80" t="s">
@@ -13252,54 +13917,54 @@
       <c r="D21" s="93"/>
       <c r="E21" s="93"/>
       <c r="F21" s="525"/>
-      <c r="G21" s="777" t="s">
+      <c r="G21" s="787" t="s">
         <v>619</v>
       </c>
-      <c r="H21" s="774"/>
-      <c r="I21" s="774"/>
+      <c r="H21" s="784"/>
+      <c r="I21" s="784"/>
       <c r="J21" s="620">
         <f>0.9*J22</f>
         <v>1428.3</v>
       </c>
-      <c r="K21" s="774" t="s">
+      <c r="K21" s="784" t="s">
         <v>695</v>
       </c>
-      <c r="L21" s="774"/>
+      <c r="L21" s="784"/>
       <c r="M21" s="623"/>
       <c r="N21" s="627">
         <f>J22*C20-L12*C21</f>
         <v>1728</v>
       </c>
-      <c r="P21" s="689" t="s">
+      <c r="P21" s="699" t="s">
         <v>698</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="768" t="s">
+      <c r="B22" s="778" t="s">
         <v>525</v>
       </c>
-      <c r="C22" s="769"/>
-      <c r="D22" s="769"/>
-      <c r="E22" s="769"/>
+      <c r="C22" s="779"/>
+      <c r="D22" s="779"/>
+      <c r="E22" s="779"/>
       <c r="F22" s="525"/>
-      <c r="G22" s="779" t="s">
+      <c r="G22" s="789" t="s">
         <v>620</v>
       </c>
-      <c r="H22" s="780"/>
-      <c r="I22" s="780"/>
+      <c r="H22" s="790"/>
+      <c r="I22" s="790"/>
       <c r="J22" s="634">
         <v>1587</v>
       </c>
-      <c r="K22" s="692" t="s">
+      <c r="K22" s="702" t="s">
         <v>696</v>
       </c>
-      <c r="L22" s="692"/>
+      <c r="L22" s="702"/>
       <c r="M22" s="629">
         <f>ROUNDUP(J9/(J21-J10/C17),0)</f>
         <v>3</v>
       </c>
       <c r="N22" s="622"/>
-      <c r="P22" s="690"/>
+      <c r="P22" s="700"/>
     </row>
     <row r="23" spans="1:16" ht="29.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F23" s="617"/>
@@ -13307,16 +13972,16 @@
       <c r="H23" s="617"/>
       <c r="I23" s="617"/>
       <c r="J23" s="617"/>
-      <c r="K23" s="779" t="s">
+      <c r="K23" s="789" t="s">
         <v>697</v>
       </c>
-      <c r="L23" s="780"/>
+      <c r="L23" s="790"/>
       <c r="M23" s="628"/>
       <c r="N23" s="621">
         <f>ROUNDUP(L9/(J22-L10/C17),0)</f>
         <v>5</v>
       </c>
-      <c r="P23" s="691"/>
+      <c r="P23" s="701"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="385"/>
@@ -13325,9 +13990,9 @@
       <c r="D24" s="386"/>
       <c r="E24" s="387"/>
       <c r="F24" s="385"/>
-      <c r="G24" s="778"/>
-      <c r="H24" s="778"/>
-      <c r="I24" s="778"/>
+      <c r="G24" s="788"/>
+      <c r="H24" s="788"/>
+      <c r="I24" s="788"/>
       <c r="J24" s="119"/>
     </row>
     <row r="25" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -13337,16 +14002,16 @@
       <c r="D25" s="386"/>
       <c r="E25" s="387"/>
       <c r="F25" s="385"/>
-      <c r="G25" s="790" t="s">
+      <c r="G25" s="800" t="s">
         <v>158</v>
       </c>
-      <c r="H25" s="791"/>
-      <c r="I25" s="791"/>
-      <c r="J25" s="791"/>
-      <c r="K25" s="791"/>
-      <c r="L25" s="791"/>
-      <c r="M25" s="791"/>
-      <c r="N25" s="792"/>
+      <c r="H25" s="801"/>
+      <c r="I25" s="801"/>
+      <c r="J25" s="801"/>
+      <c r="K25" s="801"/>
+      <c r="L25" s="801"/>
+      <c r="M25" s="801"/>
+      <c r="N25" s="802"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="385"/>
@@ -13355,11 +14020,11 @@
       <c r="D26" s="386"/>
       <c r="E26" s="387"/>
       <c r="F26" s="385"/>
-      <c r="G26" s="793" t="s">
+      <c r="G26" s="803" t="s">
         <v>154</v>
       </c>
-      <c r="H26" s="794"/>
-      <c r="I26" s="794"/>
+      <c r="H26" s="804"/>
+      <c r="I26" s="804"/>
       <c r="J26" s="280">
         <f>J28*C20</f>
         <v>4236</v>
@@ -13388,11 +14053,11 @@
       <c r="D27" s="386"/>
       <c r="E27" s="387"/>
       <c r="F27" s="385"/>
-      <c r="G27" s="772" t="s">
+      <c r="G27" s="782" t="s">
         <v>155</v>
       </c>
-      <c r="H27" s="773"/>
-      <c r="I27" s="773"/>
+      <c r="H27" s="783"/>
+      <c r="I27" s="783"/>
       <c r="J27" s="281">
         <f>IF(OR(LEFT(C10,2)="FC",LEFT(C10,2)="Ce"),ROUND(J26/C11,0),"Non")</f>
         <v>1412</v>
@@ -13421,11 +14086,11 @@
       <c r="D28" s="386"/>
       <c r="E28" s="387"/>
       <c r="F28" s="385"/>
-      <c r="G28" s="772" t="s">
+      <c r="G28" s="782" t="s">
         <v>156</v>
       </c>
-      <c r="H28" s="773"/>
-      <c r="I28" s="773"/>
+      <c r="H28" s="783"/>
+      <c r="I28" s="783"/>
       <c r="J28" s="281">
         <f>IF(I57=0,ROUND(K56/C20*1.1,0),0)</f>
         <v>353</v>
@@ -13454,11 +14119,11 @@
       <c r="D29" s="386"/>
       <c r="E29" s="387"/>
       <c r="F29" s="385"/>
-      <c r="G29" s="788" t="s">
+      <c r="G29" s="798" t="s">
         <v>157</v>
       </c>
-      <c r="H29" s="789"/>
-      <c r="I29" s="789"/>
+      <c r="H29" s="799"/>
+      <c r="I29" s="799"/>
       <c r="J29" s="279">
         <f>IF(LEFT(J27,1)="N",J27,ROUND(J27/(C17*C11),0))</f>
         <v>78</v>
@@ -13582,18 +14247,18 @@
       <c r="N34" s="93"/>
     </row>
     <row r="35" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="744" t="s">
+      <c r="A35" s="754" t="s">
         <v>128</v>
       </c>
-      <c r="B35" s="746"/>
-      <c r="C35" s="746"/>
-      <c r="D35" s="746"/>
-      <c r="E35" s="746"/>
-      <c r="F35" s="746"/>
-      <c r="G35" s="746"/>
-      <c r="H35" s="746"/>
-      <c r="I35" s="746"/>
-      <c r="J35" s="747"/>
+      <c r="B35" s="756"/>
+      <c r="C35" s="756"/>
+      <c r="D35" s="756"/>
+      <c r="E35" s="756"/>
+      <c r="F35" s="756"/>
+      <c r="G35" s="756"/>
+      <c r="H35" s="756"/>
+      <c r="I35" s="756"/>
+      <c r="J35" s="757"/>
       <c r="K35" s="75">
         <f>K60+K104</f>
         <v>4947.3343167406474</v>
@@ -13628,45 +14293,45 @@
       <c r="N36" s="486"/>
     </row>
     <row r="37" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="770" t="s">
+      <c r="A37" s="780" t="s">
         <v>587</v>
       </c>
-      <c r="B37" s="770"/>
+      <c r="B37" s="780"/>
       <c r="C37" s="488" t="s">
         <v>577</v>
       </c>
       <c r="D37" s="488" t="s">
         <v>578</v>
       </c>
-      <c r="E37" s="771" t="s">
+      <c r="E37" s="781" t="s">
         <v>576</v>
       </c>
-      <c r="F37" s="771"/>
-      <c r="G37" s="771"/>
-      <c r="H37" s="771"/>
-      <c r="I37" s="771"/>
-      <c r="J37" s="771"/>
+      <c r="F37" s="781"/>
+      <c r="G37" s="781"/>
+      <c r="H37" s="781"/>
+      <c r="I37" s="781"/>
+      <c r="J37" s="781"/>
     </row>
     <row r="38" spans="1:14" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="741" t="s">
+      <c r="A38" s="751" t="s">
         <v>124</v>
       </c>
-      <c r="B38" s="742"/>
-      <c r="C38" s="742"/>
-      <c r="D38" s="742"/>
-      <c r="E38" s="742"/>
-      <c r="F38" s="742"/>
-      <c r="G38" s="742"/>
-      <c r="H38" s="742"/>
-      <c r="I38" s="742"/>
-      <c r="J38" s="742"/>
-      <c r="K38" s="742"/>
-      <c r="L38" s="742"/>
-      <c r="M38" s="742"/>
-      <c r="N38" s="743"/>
+      <c r="B38" s="752"/>
+      <c r="C38" s="752"/>
+      <c r="D38" s="752"/>
+      <c r="E38" s="752"/>
+      <c r="F38" s="752"/>
+      <c r="G38" s="752"/>
+      <c r="H38" s="752"/>
+      <c r="I38" s="752"/>
+      <c r="J38" s="752"/>
+      <c r="K38" s="752"/>
+      <c r="L38" s="752"/>
+      <c r="M38" s="752"/>
+      <c r="N38" s="753"/>
     </row>
     <row r="39" spans="1:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="756" t="s">
+      <c r="A39" s="766" t="s">
         <v>19</v>
       </c>
       <c r="B39" s="16" t="s">
@@ -13703,7 +14368,7 @@
       </c>
     </row>
     <row r="40" spans="1:14" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="758"/>
+      <c r="A40" s="768"/>
       <c r="B40" s="18" t="s">
         <v>13</v>
       </c>
@@ -13719,7 +14384,7 @@
       <c r="I40" s="396"/>
       <c r="J40" s="401"/>
       <c r="K40" s="19">
-        <f t="shared" ref="K40:K55" si="3">SUM(E40:J40)-F40-G40</f>
+        <f t="shared" ref="K40:K55" si="0">SUM(E40:J40)-F40-G40</f>
         <v>0</v>
       </c>
       <c r="L40" s="19">
@@ -13736,7 +14401,7 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="756" t="s">
+      <c r="A41" s="766" t="s">
         <v>11</v>
       </c>
       <c r="B41" s="20" t="s">
@@ -13756,7 +14421,7 @@
       <c r="I41" s="395"/>
       <c r="J41" s="400"/>
       <c r="K41" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>256.41156626506023</v>
       </c>
       <c r="L41" s="17">
@@ -13773,7 +14438,7 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="757"/>
+      <c r="A42" s="767"/>
       <c r="B42" s="4" t="s">
         <v>3</v>
       </c>
@@ -13791,7 +14456,7 @@
       <c r="I42" s="397"/>
       <c r="J42" s="402"/>
       <c r="K42" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>512.82313253012046</v>
       </c>
       <c r="L42" s="11">
@@ -13808,7 +14473,7 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A43" s="757"/>
+      <c r="A43" s="767"/>
       <c r="B43" s="4" t="s">
         <v>4</v>
       </c>
@@ -13826,7 +14491,7 @@
       <c r="I43" s="397"/>
       <c r="J43" s="402"/>
       <c r="K43" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>512.82313253012046</v>
       </c>
       <c r="L43" s="11">
@@ -13843,7 +14508,7 @@
       </c>
     </row>
     <row r="44" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="758"/>
+      <c r="A44" s="768"/>
       <c r="B44" s="21" t="s">
         <v>5</v>
       </c>
@@ -13861,7 +14526,7 @@
       <c r="I44" s="396"/>
       <c r="J44" s="401"/>
       <c r="K44" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>512.82313253012046</v>
       </c>
       <c r="L44" s="19">
@@ -13878,7 +14543,7 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="756" t="s">
+      <c r="A45" s="766" t="s">
         <v>12</v>
       </c>
       <c r="B45" s="16" t="s">
@@ -13898,7 +14563,7 @@
       <c r="I45" s="395"/>
       <c r="J45" s="400"/>
       <c r="K45" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>1538.4693975903615</v>
       </c>
       <c r="L45" s="17">
@@ -13915,7 +14580,7 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="757"/>
+      <c r="A46" s="767"/>
       <c r="B46" s="7" t="s">
         <v>7</v>
       </c>
@@ -13931,7 +14596,7 @@
       <c r="I46" s="397"/>
       <c r="J46" s="402"/>
       <c r="K46" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L46" s="11">
@@ -13948,7 +14613,7 @@
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="757"/>
+      <c r="A47" s="767"/>
       <c r="B47" s="4" t="s">
         <v>8</v>
       </c>
@@ -13981,7 +14646,7 @@
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="757"/>
+      <c r="A48" s="767"/>
       <c r="B48" s="114" t="s">
         <v>409</v>
       </c>
@@ -14012,7 +14677,7 @@
         <v>0</v>
       </c>
       <c r="K48" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L48" s="11">
@@ -14029,7 +14694,7 @@
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A49" s="757"/>
+      <c r="A49" s="767"/>
       <c r="B49" s="490" t="s">
         <v>145</v>
       </c>
@@ -14045,7 +14710,7 @@
       <c r="I49" s="397"/>
       <c r="J49" s="402"/>
       <c r="K49" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L49" s="11">
@@ -14062,7 +14727,7 @@
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" s="757"/>
+      <c r="A50" s="767"/>
       <c r="B50" s="490" t="s">
         <v>145</v>
       </c>
@@ -14078,7 +14743,7 @@
       <c r="I50" s="397"/>
       <c r="J50" s="402"/>
       <c r="K50" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L50" s="11">
@@ -14095,7 +14760,7 @@
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" s="757"/>
+      <c r="A51" s="767"/>
       <c r="B51" s="490" t="s">
         <v>145</v>
       </c>
@@ -14111,7 +14776,7 @@
       <c r="I51" s="397"/>
       <c r="J51" s="402"/>
       <c r="K51" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L51" s="11">
@@ -14128,7 +14793,7 @@
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" s="757"/>
+      <c r="A52" s="767"/>
       <c r="B52" s="6" t="s">
         <v>9</v>
       </c>
@@ -14144,7 +14809,7 @@
       <c r="I52" s="397"/>
       <c r="J52" s="402"/>
       <c r="K52" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L52" s="11">
@@ -14161,7 +14826,7 @@
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53" s="759"/>
+      <c r="A53" s="769"/>
       <c r="B53" s="4" t="s">
         <v>10</v>
       </c>
@@ -14177,7 +14842,7 @@
       <c r="I53" s="398"/>
       <c r="J53" s="403"/>
       <c r="K53" s="44">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L53" s="11">
@@ -14194,7 +14859,7 @@
       </c>
     </row>
     <row r="54" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="759"/>
+      <c r="A54" s="769"/>
       <c r="B54" s="134" t="s">
         <v>166</v>
       </c>
@@ -14210,7 +14875,7 @@
       <c r="I54" s="399"/>
       <c r="J54" s="404"/>
       <c r="K54" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L54" s="135">
@@ -14227,7 +14892,7 @@
       </c>
     </row>
     <row r="55" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="759"/>
+      <c r="A55" s="769"/>
       <c r="B55" s="106" t="s">
         <v>24</v>
       </c>
@@ -14240,7 +14905,7 @@
       <c r="I55" s="132"/>
       <c r="J55" s="405"/>
       <c r="K55" s="133">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L55" s="44">
@@ -14257,10 +14922,10 @@
       </c>
     </row>
     <row r="56" spans="1:15" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="775" t="s">
+      <c r="A56" s="785" t="s">
         <v>15</v>
       </c>
-      <c r="B56" s="776"/>
+      <c r="B56" s="786"/>
       <c r="C56" s="45">
         <f>SUM(C39:C55)</f>
         <v>60</v>
@@ -14293,7 +14958,7 @@
         <v>7773.8858660240967</v>
       </c>
       <c r="M56" s="99">
-        <f t="shared" ref="M56" si="4">SUM(M39:M55)</f>
+        <f>SUM(M39:M55)</f>
         <v>7538.5000481927709</v>
       </c>
       <c r="N56" s="99">
@@ -14302,16 +14967,16 @@
       </c>
     </row>
     <row r="57" spans="1:15" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="748" t="s">
+      <c r="A57" s="758" t="s">
         <v>143</v>
       </c>
-      <c r="B57" s="749"/>
-      <c r="C57" s="749"/>
-      <c r="D57" s="749"/>
-      <c r="E57" s="749"/>
-      <c r="F57" s="749"/>
-      <c r="G57" s="749"/>
-      <c r="H57" s="750"/>
+      <c r="B57" s="759"/>
+      <c r="C57" s="759"/>
+      <c r="D57" s="759"/>
+      <c r="E57" s="759"/>
+      <c r="F57" s="759"/>
+      <c r="G57" s="759"/>
+      <c r="H57" s="760"/>
       <c r="I57" s="512">
         <v>0</v>
       </c>
@@ -14320,10 +14985,10 @@
       <c r="L57" s="111"/>
     </row>
     <row r="58" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="744" t="s">
+      <c r="A58" s="754" t="s">
         <v>123</v>
       </c>
-      <c r="B58" s="745"/>
+      <c r="B58" s="755"/>
       <c r="C58" s="45">
         <f>IF(I57=0,0,ROUND(C56/I57,0))</f>
         <v>0</v>
@@ -14369,11 +15034,11 @@
       <c r="C59" s="483"/>
       <c r="D59" s="483"/>
       <c r="E59" s="483"/>
-      <c r="F59" s="751" t="s">
+      <c r="F59" s="761" t="s">
         <v>126</v>
       </c>
-      <c r="G59" s="752"/>
-      <c r="H59" s="753"/>
+      <c r="G59" s="762"/>
+      <c r="H59" s="763"/>
       <c r="I59" s="513">
         <f>C18</f>
         <v>2</v>
@@ -14383,10 +15048,10 @@
       <c r="L59" s="484"/>
     </row>
     <row r="60" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="744" t="s">
+      <c r="A60" s="754" t="s">
         <v>127</v>
       </c>
-      <c r="B60" s="745"/>
+      <c r="B60" s="755"/>
       <c r="C60" s="45">
         <f>ROUND(C58/I59,0)</f>
         <v>0</v>
@@ -14445,45 +15110,45 @@
       <c r="O61" s="118"/>
     </row>
     <row r="62" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="770" t="s">
+      <c r="A62" s="780" t="s">
         <v>586</v>
       </c>
-      <c r="B62" s="770"/>
+      <c r="B62" s="780"/>
       <c r="C62" s="488" t="s">
         <v>577</v>
       </c>
       <c r="D62" s="488" t="s">
         <v>578</v>
       </c>
-      <c r="E62" s="771" t="s">
+      <c r="E62" s="781" t="s">
         <v>576</v>
       </c>
-      <c r="F62" s="771"/>
-      <c r="G62" s="771"/>
-      <c r="H62" s="771"/>
-      <c r="I62" s="771"/>
-      <c r="J62" s="771"/>
+      <c r="F62" s="781"/>
+      <c r="G62" s="781"/>
+      <c r="H62" s="781"/>
+      <c r="I62" s="781"/>
+      <c r="J62" s="781"/>
     </row>
     <row r="63" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="741" t="s">
+      <c r="A63" s="751" t="s">
         <v>125</v>
       </c>
-      <c r="B63" s="742"/>
-      <c r="C63" s="742"/>
-      <c r="D63" s="742"/>
-      <c r="E63" s="742"/>
-      <c r="F63" s="742"/>
-      <c r="G63" s="742"/>
-      <c r="H63" s="742"/>
-      <c r="I63" s="742"/>
-      <c r="J63" s="742"/>
-      <c r="K63" s="742"/>
-      <c r="L63" s="742"/>
-      <c r="M63" s="742"/>
-      <c r="N63" s="743"/>
+      <c r="B63" s="752"/>
+      <c r="C63" s="752"/>
+      <c r="D63" s="752"/>
+      <c r="E63" s="752"/>
+      <c r="F63" s="752"/>
+      <c r="G63" s="752"/>
+      <c r="H63" s="752"/>
+      <c r="I63" s="752"/>
+      <c r="J63" s="752"/>
+      <c r="K63" s="752"/>
+      <c r="L63" s="752"/>
+      <c r="M63" s="752"/>
+      <c r="N63" s="753"/>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A64" s="757" t="s">
+      <c r="A64" s="767" t="s">
         <v>29</v>
       </c>
       <c r="B64" s="83" t="s">
@@ -14501,7 +15166,7 @@
       <c r="I64" s="408"/>
       <c r="J64" s="409"/>
       <c r="K64" s="84">
-        <f t="shared" ref="K64:K82" si="5">SUM(E64:J64)-F64-G64</f>
+        <f t="shared" ref="K64:K82" si="1">SUM(E64:J64)-F64-G64</f>
         <v>0</v>
       </c>
       <c r="L64" s="91">
@@ -14518,7 +15183,7 @@
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A65" s="757"/>
+      <c r="A65" s="767"/>
       <c r="B65" s="4" t="s">
         <v>31</v>
       </c>
@@ -14534,7 +15199,7 @@
       <c r="I65" s="397"/>
       <c r="J65" s="402"/>
       <c r="K65" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L65" s="44">
@@ -14551,7 +15216,7 @@
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A66" s="757"/>
+      <c r="A66" s="767"/>
       <c r="B66" s="4" t="s">
         <v>32</v>
       </c>
@@ -14567,7 +15232,7 @@
       <c r="I66" s="397"/>
       <c r="J66" s="402"/>
       <c r="K66" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L66" s="44">
@@ -14584,7 +15249,7 @@
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A67" s="757"/>
+      <c r="A67" s="767"/>
       <c r="B67" s="4" t="s">
         <v>33</v>
       </c>
@@ -14602,7 +15267,7 @@
       <c r="I67" s="397"/>
       <c r="J67" s="402"/>
       <c r="K67" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>128.20578313253012</v>
       </c>
       <c r="L67" s="44">
@@ -14619,7 +15284,7 @@
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A68" s="757"/>
+      <c r="A68" s="767"/>
       <c r="B68" s="4" t="s">
         <v>34</v>
       </c>
@@ -14635,7 +15300,7 @@
       <c r="I68" s="397"/>
       <c r="J68" s="402"/>
       <c r="K68" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L68" s="44">
@@ -14652,7 +15317,7 @@
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A69" s="755"/>
+      <c r="A69" s="765"/>
       <c r="B69" s="5" t="s">
         <v>35</v>
       </c>
@@ -14668,7 +15333,7 @@
       <c r="I69" s="397"/>
       <c r="J69" s="402"/>
       <c r="K69" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L69" s="44">
@@ -14685,7 +15350,7 @@
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A70" s="760" t="s">
+      <c r="A70" s="770" t="s">
         <v>147</v>
       </c>
       <c r="B70" s="490" t="s">
@@ -14705,7 +15370,7 @@
       <c r="I70" s="397"/>
       <c r="J70" s="402"/>
       <c r="K70" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>128.20578313253012</v>
       </c>
       <c r="L70" s="44">
@@ -14722,7 +15387,7 @@
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A71" s="761"/>
+      <c r="A71" s="771"/>
       <c r="B71" s="490" t="s">
         <v>148</v>
       </c>
@@ -14738,7 +15403,7 @@
       <c r="I71" s="397"/>
       <c r="J71" s="402"/>
       <c r="K71" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L71" s="44">
@@ -14755,7 +15420,7 @@
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A72" s="761"/>
+      <c r="A72" s="771"/>
       <c r="B72" s="490" t="s">
         <v>148</v>
       </c>
@@ -14771,7 +15436,7 @@
       <c r="I72" s="397"/>
       <c r="J72" s="402"/>
       <c r="K72" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L72" s="44">
@@ -14788,7 +15453,7 @@
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A73" s="761"/>
+      <c r="A73" s="771"/>
       <c r="B73" s="490" t="s">
         <v>148</v>
       </c>
@@ -14804,7 +15469,7 @@
       <c r="I73" s="397"/>
       <c r="J73" s="402"/>
       <c r="K73" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L73" s="44">
@@ -14821,7 +15486,7 @@
       </c>
     </row>
     <row r="74" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="762"/>
+      <c r="A74" s="772"/>
       <c r="B74" s="490" t="s">
         <v>148</v>
       </c>
@@ -14837,7 +15502,7 @@
       <c r="I74" s="397"/>
       <c r="J74" s="402"/>
       <c r="K74" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L74" s="44">
@@ -14854,7 +15519,7 @@
       </c>
     </row>
     <row r="75" spans="1:14" ht="30.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="754" t="s">
+      <c r="A75" s="764" t="s">
         <v>36</v>
       </c>
       <c r="B75" s="367" t="s">
@@ -14870,7 +15535,7 @@
         <f>C75*VLOOKUP(C62,A115:C148,3,FALSE)+VLOOKUP(D62,A115:C144,3,FALSE)*D75</f>
         <v>107.7702599873177</v>
       </c>
-      <c r="F75" s="873">
+      <c r="F75" s="642">
         <f>7.25+11.5*2</f>
         <v>30.25</v>
       </c>
@@ -14899,7 +15564,7 @@
       </c>
     </row>
     <row r="76" spans="1:14" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="757"/>
+      <c r="A76" s="767"/>
       <c r="B76" s="506" t="s">
         <v>605</v>
       </c>
@@ -14918,7 +15583,7 @@
       <c r="I76" s="397"/>
       <c r="J76" s="403"/>
       <c r="K76" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L76" s="44">
@@ -14935,7 +15600,7 @@
       </c>
     </row>
     <row r="77" spans="1:14" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="763"/>
+      <c r="A77" s="773"/>
       <c r="B77" s="4" t="s">
         <v>560</v>
       </c>
@@ -14948,7 +15613,7 @@
       <c r="I77" s="108"/>
       <c r="J77" s="410"/>
       <c r="K77" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L77" s="44">
@@ -14965,7 +15630,7 @@
       </c>
     </row>
     <row r="78" spans="1:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="754" t="s">
+      <c r="A78" s="764" t="s">
         <v>44</v>
       </c>
       <c r="B78" s="83" t="s">
@@ -14983,7 +15648,7 @@
       <c r="I78" s="397"/>
       <c r="J78" s="409"/>
       <c r="K78" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L78" s="44">
@@ -15000,7 +15665,7 @@
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A79" s="755"/>
+      <c r="A79" s="765"/>
       <c r="B79" s="4" t="s">
         <v>46</v>
       </c>
@@ -15016,7 +15681,7 @@
       <c r="I79" s="397"/>
       <c r="J79" s="402"/>
       <c r="K79" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L79" s="44">
@@ -15033,16 +15698,16 @@
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A80" s="754" t="s">
+      <c r="A80" s="764" t="s">
         <v>47</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C80" s="872">
+      <c r="C80" s="641">
         <v>2</v>
       </c>
-      <c r="D80" s="872">
+      <c r="D80" s="641">
         <v>5</v>
       </c>
       <c r="E80" s="11">
@@ -15055,7 +15720,7 @@
       <c r="I80" s="397"/>
       <c r="J80" s="402"/>
       <c r="K80" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>346.54262523779329</v>
       </c>
       <c r="L80" s="44">
@@ -15072,12 +15737,12 @@
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A81" s="755"/>
+      <c r="A81" s="765"/>
       <c r="B81" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C81" s="872"/>
-      <c r="D81" s="872">
+      <c r="C81" s="641"/>
+      <c r="D81" s="641">
         <v>2</v>
       </c>
       <c r="E81" s="11">
@@ -15090,7 +15755,7 @@
       <c r="I81" s="397"/>
       <c r="J81" s="402"/>
       <c r="K81" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>87.334736842105272</v>
       </c>
       <c r="L81" s="44">
@@ -15125,7 +15790,7 @@
         <v>0</v>
       </c>
       <c r="K82" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L82" s="44">
@@ -15194,7 +15859,7 @@
       <c r="I84" s="402"/>
       <c r="J84" s="402"/>
       <c r="K84" s="11">
-        <f t="shared" ref="K84:K103" si="6">SUM(E84:J84)-F84-G84</f>
+        <f t="shared" ref="K84:K103" si="2">SUM(E84:J84)-F84-G84</f>
         <v>0</v>
       </c>
       <c r="L84" s="44">
@@ -15227,7 +15892,7 @@
         <v>400</v>
       </c>
       <c r="K85" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>400</v>
       </c>
       <c r="L85" s="44">
@@ -15257,7 +15922,7 @@
       <c r="I86" s="402"/>
       <c r="J86" s="402"/>
       <c r="K86" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L86" s="44">
@@ -15274,7 +15939,7 @@
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A87" s="754" t="s">
+      <c r="A87" s="764" t="s">
         <v>102</v>
       </c>
       <c r="B87" s="4" t="s">
@@ -15292,7 +15957,7 @@
         <v>0</v>
       </c>
       <c r="K87" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L87" s="44">
@@ -15309,7 +15974,7 @@
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A88" s="757"/>
+      <c r="A88" s="767"/>
       <c r="B88" s="4" t="s">
         <v>90</v>
       </c>
@@ -15325,7 +15990,7 @@
         <v>187.5</v>
       </c>
       <c r="K88" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>187.5</v>
       </c>
       <c r="L88" s="44">
@@ -15342,7 +16007,7 @@
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A89" s="757"/>
+      <c r="A89" s="767"/>
       <c r="B89" s="4" t="s">
         <v>96</v>
       </c>
@@ -15358,7 +16023,7 @@
         <v>0</v>
       </c>
       <c r="K89" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L89" s="44">
@@ -15375,7 +16040,7 @@
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A90" s="757"/>
+      <c r="A90" s="767"/>
       <c r="B90" s="5" t="s">
         <v>101</v>
       </c>
@@ -15391,7 +16056,7 @@
         <v>0</v>
       </c>
       <c r="K90" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L90" s="44">
@@ -15408,7 +16073,7 @@
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A91" s="757"/>
+      <c r="A91" s="767"/>
       <c r="B91" s="5" t="s">
         <v>100</v>
       </c>
@@ -15424,7 +16089,7 @@
         <v>337.55999999999995</v>
       </c>
       <c r="K91" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>337.55999999999995</v>
       </c>
       <c r="L91" s="44">
@@ -15441,7 +16106,7 @@
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A92" s="757"/>
+      <c r="A92" s="767"/>
       <c r="B92" s="113" t="str">
         <f>'Coûts frais variables'!A18</f>
         <v>Accès aux télémanipulateurs</v>
@@ -15458,7 +16123,7 @@
         <v>1200</v>
       </c>
       <c r="K92" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>1200</v>
       </c>
       <c r="L92" s="44">
@@ -15475,7 +16140,7 @@
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A93" s="757"/>
+      <c r="A93" s="767"/>
       <c r="B93" s="113" t="str">
         <f>'Coûts frais variables'!A19</f>
         <v>Libellé libre frais variable à saisir si besoin (onglet frais var)</v>
@@ -15492,7 +16157,7 @@
         <v>0</v>
       </c>
       <c r="K93" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L93" s="44">
@@ -15509,7 +16174,7 @@
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A94" s="757"/>
+      <c r="A94" s="767"/>
       <c r="B94" s="113" t="str">
         <f>'Coûts frais variables'!A20</f>
         <v>Libellé libre frais variable à saisir si besoin (onglet frais var)</v>
@@ -15526,7 +16191,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L94" s="44">
@@ -15543,7 +16208,7 @@
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A95" s="757"/>
+      <c r="A95" s="767"/>
       <c r="B95" s="113" t="str">
         <f>'Coûts frais variables'!A21</f>
         <v>Libellé libre frais variable à saisir si besoin (onglet frais var)</v>
@@ -15560,7 +16225,7 @@
         <v>0</v>
       </c>
       <c r="K95" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L95" s="44">
@@ -15577,7 +16242,7 @@
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A96" s="754" t="s">
+      <c r="A96" s="764" t="s">
         <v>121</v>
       </c>
       <c r="B96" s="4" t="s">
@@ -15595,7 +16260,7 @@
       <c r="I96" s="397"/>
       <c r="J96" s="402"/>
       <c r="K96" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L96" s="44">
@@ -15612,7 +16277,7 @@
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A97" s="757"/>
+      <c r="A97" s="767"/>
       <c r="B97" s="7" t="s">
         <v>120</v>
       </c>
@@ -15628,7 +16293,7 @@
       <c r="I97" s="397"/>
       <c r="J97" s="402"/>
       <c r="K97" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L97" s="44">
@@ -15645,14 +16310,14 @@
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A98" s="757"/>
+      <c r="A98" s="767"/>
       <c r="B98" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="C98" s="872">
+      <c r="C98" s="641">
         <v>1</v>
       </c>
-      <c r="D98" s="872">
+      <c r="D98" s="641">
         <v>2</v>
       </c>
       <c r="E98" s="11">
@@ -15665,7 +16330,7 @@
       <c r="I98" s="397"/>
       <c r="J98" s="402"/>
       <c r="K98" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>151.43762840837033</v>
       </c>
       <c r="L98" s="44">
@@ -15682,12 +16347,12 @@
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A99" s="757"/>
+      <c r="A99" s="767"/>
       <c r="B99" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="C99" s="872"/>
-      <c r="D99" s="872"/>
+      <c r="C99" s="641"/>
+      <c r="D99" s="641"/>
       <c r="E99" s="11">
         <f>C99*VLOOKUP(C62,A115:C148,3,FALSE)+VLOOKUP(D62,A115:C144,3,FALSE)*D99</f>
         <v>0</v>
@@ -15698,7 +16363,7 @@
       <c r="I99" s="397"/>
       <c r="J99" s="402"/>
       <c r="K99" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L99" s="44">
@@ -15715,12 +16380,12 @@
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A100" s="757"/>
+      <c r="A100" s="767"/>
       <c r="B100" s="4" t="s">
         <v>600</v>
       </c>
-      <c r="C100" s="872"/>
-      <c r="D100" s="872"/>
+      <c r="C100" s="641"/>
+      <c r="D100" s="641"/>
       <c r="E100" s="11">
         <f>C100*VLOOKUP(C62,A115:C148,3,FALSE)+VLOOKUP(D62,A115:C144,3,FALSE)*D100</f>
         <v>0</v>
@@ -15731,7 +16396,7 @@
       <c r="I100" s="397"/>
       <c r="J100" s="402"/>
       <c r="K100" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L100" s="44">
@@ -15748,7 +16413,7 @@
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A101" s="757"/>
+      <c r="A101" s="767"/>
       <c r="B101" s="6" t="s">
         <v>601</v>
       </c>
@@ -15761,7 +16426,7 @@
       <c r="I101" s="397"/>
       <c r="J101" s="402"/>
       <c r="K101" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L101" s="44">
@@ -15778,7 +16443,7 @@
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A102" s="757"/>
+      <c r="A102" s="767"/>
       <c r="B102" s="4" t="s">
         <v>118</v>
       </c>
@@ -15794,7 +16459,7 @@
       <c r="I102" s="397"/>
       <c r="J102" s="402"/>
       <c r="K102" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L102" s="44">
@@ -15811,7 +16476,7 @@
       </c>
     </row>
     <row r="103" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="757"/>
+      <c r="A103" s="767"/>
       <c r="B103" s="2" t="s">
         <v>119</v>
       </c>
@@ -15824,7 +16489,7 @@
       <c r="I103" s="403"/>
       <c r="J103" s="398"/>
       <c r="K103" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L103" s="44">
@@ -15841,56 +16506,56 @@
       </c>
     </row>
     <row r="104" spans="1:14" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="744" t="s">
+      <c r="A104" s="754" t="s">
         <v>28</v>
       </c>
-      <c r="B104" s="745"/>
+      <c r="B104" s="755"/>
       <c r="C104" s="45">
-        <f>SUM(C64:C103)</f>
+        <f t="shared" ref="C104:N104" si="3">SUM(C64:C103)</f>
         <v>8</v>
       </c>
       <c r="D104" s="45">
-        <f>SUM(D64:D103)</f>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="E104" s="46">
-        <f>SUM(E64:E103)</f>
+        <f t="shared" si="3"/>
         <v>949.49681674064686</v>
       </c>
       <c r="F104" s="46">
-        <f>SUM(F64:F103)</f>
+        <f t="shared" si="3"/>
         <v>30.25</v>
       </c>
       <c r="G104" s="46">
-        <f>SUM(G64:G103)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H104" s="46">
-        <f t="shared" ref="H104:J104" si="7">SUM(H64:H103)</f>
+        <f t="shared" si="3"/>
         <v>1872.7775000000001</v>
       </c>
       <c r="I104" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J104" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>2125.06</v>
       </c>
       <c r="K104" s="46">
-        <f>SUM(K64:K103)</f>
+        <f t="shared" si="3"/>
         <v>4947.3343167406474</v>
       </c>
       <c r="L104" s="46">
-        <f>SUM(L64:L103)</f>
+        <f t="shared" si="3"/>
         <v>7868.4147177461964</v>
       </c>
       <c r="M104" s="99">
-        <f>SUM(M64:M103)</f>
+        <f t="shared" si="3"/>
         <v>7656.7176608116679</v>
       </c>
       <c r="N104" s="99">
-        <f>SUM(N64:N103)</f>
+        <f t="shared" si="3"/>
         <v>6306.1255661283831</v>
       </c>
     </row>
@@ -15918,28 +16583,28 @@
       </c>
     </row>
     <row r="113" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G113" s="724" t="str">
+      <c r="G113" s="734" t="str">
         <f>CONCATENATE("Tarifs applicables en cas d'utilisation pluriannuelle de cette fiche de coûts (application d'un coefficient de dérive annuelle de ",C128*100, " % à la phase de réalisation (phase de conception exclue car effectuée en année 1) :")</f>
         <v>Tarifs applicables en cas d'utilisation pluriannuelle de cette fiche de coûts (application d'un coefficient de dérive annuelle de 1,9 % à la phase de réalisation (phase de conception exclue car effectuée en année 1) :</v>
       </c>
-      <c r="H113" s="725"/>
-      <c r="I113" s="725"/>
-      <c r="J113" s="725"/>
-      <c r="K113" s="725"/>
-      <c r="L113" s="725"/>
-      <c r="M113" s="726"/>
+      <c r="H113" s="735"/>
+      <c r="I113" s="735"/>
+      <c r="J113" s="735"/>
+      <c r="K113" s="735"/>
+      <c r="L113" s="735"/>
+      <c r="M113" s="736"/>
     </row>
     <row r="114" spans="1:13" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C114" s="271" t="s">
         <v>43</v>
       </c>
-      <c r="G114" s="727"/>
-      <c r="H114" s="728"/>
-      <c r="I114" s="728"/>
-      <c r="J114" s="728"/>
-      <c r="K114" s="728"/>
-      <c r="L114" s="728"/>
-      <c r="M114" s="729"/>
+      <c r="G114" s="737"/>
+      <c r="H114" s="738"/>
+      <c r="I114" s="738"/>
+      <c r="J114" s="738"/>
+      <c r="K114" s="738"/>
+      <c r="L114" s="738"/>
+      <c r="M114" s="739"/>
     </row>
     <row r="115" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="93" t="s">
@@ -15954,20 +16619,20 @@
       </c>
       <c r="G115" s="126"/>
       <c r="H115" s="127"/>
-      <c r="I115" s="732" t="s">
+      <c r="I115" s="742" t="s">
         <v>16</v>
       </c>
-      <c r="J115" s="732" t="s">
+      <c r="J115" s="742" t="s">
         <v>17</v>
       </c>
-      <c r="K115" s="732" t="str">
+      <c r="K115" s="742" t="str">
         <f>CONCATENATE("Prix de vente hors CEA préconisé avec taux de marge de ",C19*100,"%")</f>
         <v>Prix de vente hors CEA préconisé avec taux de marge de 10%</v>
       </c>
-      <c r="L115" s="734" t="s">
+      <c r="L115" s="744" t="s">
         <v>152</v>
       </c>
-      <c r="M115" s="736" t="s">
+      <c r="M115" s="746" t="s">
         <v>163</v>
       </c>
     </row>
@@ -15984,11 +16649,11 @@
       </c>
       <c r="G116" s="124"/>
       <c r="H116" s="118"/>
-      <c r="I116" s="733"/>
-      <c r="J116" s="733"/>
-      <c r="K116" s="733"/>
-      <c r="L116" s="735"/>
-      <c r="M116" s="737"/>
+      <c r="I116" s="743"/>
+      <c r="J116" s="743"/>
+      <c r="K116" s="743"/>
+      <c r="L116" s="745"/>
+      <c r="M116" s="747"/>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B117" s="552" t="str">
@@ -15998,19 +16663,19 @@
       <c r="C117" s="553">
         <v>1.0212000000000001</v>
       </c>
-      <c r="D117" s="693" t="s">
+      <c r="D117" s="703" t="s">
         <v>647</v>
       </c>
-      <c r="E117" s="694"/>
-      <c r="G117" s="730" t="s">
+      <c r="E117" s="704"/>
+      <c r="G117" s="740" t="s">
         <v>164</v>
       </c>
-      <c r="H117" s="731"/>
-      <c r="I117" s="733"/>
-      <c r="J117" s="733"/>
-      <c r="K117" s="733"/>
-      <c r="L117" s="735"/>
-      <c r="M117" s="737"/>
+      <c r="H117" s="741"/>
+      <c r="I117" s="743"/>
+      <c r="J117" s="743"/>
+      <c r="K117" s="743"/>
+      <c r="L117" s="745"/>
+      <c r="M117" s="747"/>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B118" s="552" t="str">
@@ -16020,15 +16685,15 @@
       <c r="C118" s="553">
         <v>1.0057</v>
       </c>
-      <c r="D118" s="695"/>
-      <c r="E118" s="696"/>
+      <c r="D118" s="705"/>
+      <c r="E118" s="706"/>
       <c r="G118" s="124"/>
       <c r="H118" s="118"/>
-      <c r="I118" s="733"/>
-      <c r="J118" s="733"/>
-      <c r="K118" s="733"/>
-      <c r="L118" s="735"/>
-      <c r="M118" s="737"/>
+      <c r="I118" s="743"/>
+      <c r="J118" s="743"/>
+      <c r="K118" s="743"/>
+      <c r="L118" s="745"/>
+      <c r="M118" s="747"/>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B119" s="5" t="s">
@@ -16040,11 +16705,11 @@
       </c>
       <c r="G119" s="124"/>
       <c r="H119" s="118"/>
-      <c r="I119" s="733"/>
-      <c r="J119" s="733"/>
-      <c r="K119" s="733"/>
-      <c r="L119" s="735"/>
-      <c r="M119" s="737"/>
+      <c r="I119" s="743"/>
+      <c r="J119" s="743"/>
+      <c r="K119" s="743"/>
+      <c r="L119" s="745"/>
+      <c r="M119" s="747"/>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B120" s="554" t="s">
@@ -16053,15 +16718,15 @@
       <c r="C120" s="553">
         <v>1.5599999999999999E-2</v>
       </c>
-      <c r="D120" s="693" t="s">
+      <c r="D120" s="703" t="s">
         <v>647</v>
       </c>
-      <c r="E120" s="694"/>
-      <c r="G120" s="738" t="str">
+      <c r="E120" s="704"/>
+      <c r="G120" s="748" t="str">
         <f>CONCATENATE("Prix par participant ",C112)</f>
         <v>Prix par participant 2024</v>
       </c>
-      <c r="H120" s="739"/>
+      <c r="H120" s="749"/>
       <c r="I120" s="121">
         <f>J13</f>
         <v>907</v>
@@ -16090,13 +16755,13 @@
       <c r="C121" s="553">
         <v>3.4299999999999997E-2</v>
       </c>
-      <c r="D121" s="695"/>
-      <c r="E121" s="696"/>
-      <c r="G121" s="738" t="str">
+      <c r="D121" s="705"/>
+      <c r="E121" s="706"/>
+      <c r="G121" s="748" t="str">
         <f>CONCATENATE("Prix par participant ",C112+1)</f>
         <v>Prix par participant 2025</v>
       </c>
-      <c r="H121" s="739"/>
+      <c r="H121" s="749"/>
       <c r="I121" s="22">
         <f>ROUND((K35-K104+K104*(1+C128))*1.1/C17,0)</f>
         <v>924</v>
@@ -16125,11 +16790,11 @@
         <v>82.460000000000008</v>
       </c>
       <c r="D122" s="559"/>
-      <c r="G122" s="738" t="str">
+      <c r="G122" s="748" t="str">
         <f>CONCATENATE("Prix par participant ",C112+2)</f>
         <v>Prix par participant 2026</v>
       </c>
-      <c r="H122" s="739"/>
+      <c r="H122" s="749"/>
       <c r="I122" s="22">
         <f>ROUND((K35-K104+K104*(1+C128)*(1+C128))*1.1/C17,0)</f>
         <v>942</v>
@@ -16158,11 +16823,11 @@
         <v>61.910000000000004</v>
       </c>
       <c r="D123" s="559"/>
-      <c r="G123" s="738" t="str">
+      <c r="G123" s="748" t="str">
         <f>CONCATENATE("Prix par participant ",C112+3)</f>
         <v>Prix par participant 2027</v>
       </c>
-      <c r="H123" s="739"/>
+      <c r="H123" s="749"/>
       <c r="I123" s="22">
         <f>ROUND((K35-K104+K104*(1+C128)*(1+C128)*(1+C128))*1.1/C17,0)</f>
         <v>960</v>
@@ -16189,11 +16854,11 @@
       <c r="C124" s="149">
         <v>40.770000000000003</v>
       </c>
-      <c r="G124" s="738" t="str">
+      <c r="G124" s="748" t="str">
         <f>CONCATENATE("Prix par participant ",C112+4)</f>
         <v>Prix par participant 2028</v>
       </c>
-      <c r="H124" s="739"/>
+      <c r="H124" s="749"/>
       <c r="I124" s="22">
         <f>ROUND((K35-K104+K104*(1+C128)*(1+C128)*(1+C128)*(1+C128))*1.1/C17,0)</f>
         <v>978</v>
@@ -16220,11 +16885,11 @@
       <c r="C125" s="149">
         <v>31.71</v>
       </c>
-      <c r="G125" s="722" t="str">
+      <c r="G125" s="732" t="str">
         <f>CONCATENATE("Prix par participant ",C112+5)</f>
         <v>Prix par participant 2029</v>
       </c>
-      <c r="H125" s="723"/>
+      <c r="H125" s="733"/>
       <c r="I125" s="129">
         <f>ROUND((K35-K104+K104*(1+C128)*(1+C128)*(1+C128)*(1+C128)*(1+C128))*1.1/C17,0)</f>
         <v>997</v>
@@ -16251,16 +16916,16 @@
       <c r="C126" s="555">
         <v>0.96</v>
       </c>
-      <c r="D126" s="822"/>
-      <c r="E126" s="823"/>
+      <c r="D126" s="832"/>
+      <c r="E126" s="833"/>
     </row>
     <row r="127" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="B127" s="5" t="s">
         <v>628</v>
       </c>
       <c r="C127" s="551"/>
-      <c r="D127" s="824"/>
-      <c r="E127" s="825"/>
+      <c r="D127" s="834"/>
+      <c r="E127" s="835"/>
     </row>
     <row r="128" spans="1:13" collapsed="1" x14ac:dyDescent="0.25">
       <c r="B128" s="554" t="s">
@@ -16269,11 +16934,11 @@
       <c r="C128" s="553">
         <v>1.9E-2</v>
       </c>
-      <c r="D128" s="813" t="s">
+      <c r="D128" s="823" t="s">
         <v>654</v>
       </c>
-      <c r="E128" s="814"/>
-      <c r="F128" s="815"/>
+      <c r="E128" s="824"/>
+      <c r="F128" s="825"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B130" s="478" t="s">
@@ -16314,10 +16979,10 @@
       <c r="C134" s="554">
         <v>47.45</v>
       </c>
-      <c r="D134" s="816" t="s">
+      <c r="D134" s="826" t="s">
         <v>647</v>
       </c>
-      <c r="E134" s="817"/>
+      <c r="E134" s="827"/>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="93" t="s">
@@ -16329,8 +16994,8 @@
       <c r="C135" s="554">
         <v>60.57</v>
       </c>
-      <c r="D135" s="818"/>
-      <c r="E135" s="819"/>
+      <c r="D135" s="828"/>
+      <c r="E135" s="829"/>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="93" t="s">
@@ -16342,8 +17007,8 @@
       <c r="C136" s="554">
         <v>76.819999999999993</v>
       </c>
-      <c r="D136" s="820"/>
-      <c r="E136" s="821"/>
+      <c r="D136" s="830"/>
+      <c r="E136" s="831"/>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B138" s="478" t="s">
@@ -16384,10 +17049,10 @@
       <c r="C142" s="554">
         <v>30.14</v>
       </c>
-      <c r="D142" s="816" t="s">
+      <c r="D142" s="826" t="s">
         <v>647</v>
       </c>
-      <c r="E142" s="817"/>
+      <c r="E142" s="827"/>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="93" t="s">
@@ -16399,8 +17064,8 @@
       <c r="C143" s="554">
         <v>38.619999999999997</v>
       </c>
-      <c r="D143" s="818"/>
-      <c r="E143" s="819"/>
+      <c r="D143" s="828"/>
+      <c r="E143" s="829"/>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="93" t="s">
@@ -16412,8 +17077,8 @@
       <c r="C144" s="554">
         <v>48.21</v>
       </c>
-      <c r="D144" s="820"/>
-      <c r="E144" s="821"/>
+      <c r="D144" s="830"/>
+      <c r="E144" s="831"/>
     </row>
     <row r="146" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A146" s="93" t="s">
@@ -16540,7 +17205,7 @@
     <mergeCell ref="D120:E121"/>
     <mergeCell ref="C12:D12"/>
   </mergeCells>
-  <dataValidations count="4">
+  <dataValidations disablePrompts="1" count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C16" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Choisir Unité,UEC,UEFG,UECC,UEM,UES,SFRES,DIR,DSTG,DFI"</formula1>
     </dataValidation>
@@ -16563,7 +17228,7 @@
   <legacyDrawing r:id="rId4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0300-000004000000}">
           <x14:formula1>
             <xm:f>'Table FD&amp;FC'!$U$3:$U$98</xm:f>
@@ -16577,6 +17242,276 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22B8504F-C106-4C62-979B-A8F761CCE00A}">
+  <dimension ref="A1:H33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="36.5703125" customWidth="1"/>
+    <col min="3" max="3" width="50.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>720</v>
+      </c>
+      <c r="F1" t="s">
+        <v>718</v>
+      </c>
+      <c r="G1" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>721</v>
+      </c>
+      <c r="B2" t="s">
+        <v>714</v>
+      </c>
+      <c r="C2" t="s">
+        <v>715</v>
+      </c>
+      <c r="D2" t="s">
+        <v>716</v>
+      </c>
+      <c r="E2" s="647">
+        <f>F2</f>
+        <v>1725.06</v>
+      </c>
+      <c r="F2" s="647">
+        <f>SUM('Coûts frais variables'!E4:E9,'Coûts frais variables'!E14:E21)</f>
+        <v>1725.06</v>
+      </c>
+      <c r="G2" s="646">
+        <f>SUMPRODUCT('Coûts frais variables'!B4:B9,'Coûts frais variables'!C4:C9)+SUMPRODUCT('Coûts frais variables'!B14:B21,'Coûts frais variables'!C14:C21)</f>
+        <v>275.23</v>
+      </c>
+      <c r="H2" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>722</v>
+      </c>
+      <c r="B3" t="s">
+        <v>724</v>
+      </c>
+      <c r="E3" s="647">
+        <f>'Fiche de coûts'!K56</f>
+        <v>3846.1734939759035</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>723</v>
+      </c>
+      <c r="B4" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="648" t="s">
+        <v>725</v>
+      </c>
+      <c r="E9" t="s">
+        <v>720</v>
+      </c>
+      <c r="F9" t="s">
+        <v>718</v>
+      </c>
+      <c r="G9" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>721</v>
+      </c>
+      <c r="B10" t="s">
+        <v>714</v>
+      </c>
+      <c r="C10" t="s">
+        <v>730</v>
+      </c>
+      <c r="D10" t="s">
+        <v>716</v>
+      </c>
+      <c r="E10" s="649">
+        <f>F10</f>
+        <v>296.71031999999997</v>
+      </c>
+      <c r="F10" s="649">
+        <f>SUM('Fiche de coûts'!$L$88:$L$95)/'Fiche de coûts'!C17</f>
+        <v>296.71031999999997</v>
+      </c>
+      <c r="G10" s="646">
+        <f>F10</f>
+        <v>296.71031999999997</v>
+      </c>
+      <c r="H10" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>722</v>
+      </c>
+      <c r="B11" t="s">
+        <v>724</v>
+      </c>
+      <c r="C11" t="s">
+        <v>728</v>
+      </c>
+      <c r="E11" s="647">
+        <f>'Fiche de coûts'!K64</f>
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>723</v>
+      </c>
+      <c r="B12" t="s">
+        <v>724</v>
+      </c>
+      <c r="C12" t="s">
+        <v>729</v>
+      </c>
+      <c r="E12" s="650">
+        <f>'Fiche de coûts'!L9-0</f>
+        <v>6090.7380800000001</v>
+      </c>
+      <c r="G12" s="650">
+        <f>SUM('Fiche de coûts'!$L$64:$L$86,'Fiche de coûts'!$L$96:$L$103)</f>
+        <v>6088.1527977461956</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>731</v>
+      </c>
+      <c r="B13" t="s">
+        <v>724</v>
+      </c>
+      <c r="C13" t="s">
+        <v>732</v>
+      </c>
+      <c r="E13" s="645">
+        <f>E11+E12</f>
+        <v>6090.7380800000001</v>
+      </c>
+      <c r="G13" s="645">
+        <f>G11+G12</f>
+        <v>6088.1527977461956</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>734</v>
+      </c>
+      <c r="C15" t="s">
+        <v>735</v>
+      </c>
+      <c r="G15" s="646">
+        <f>'Fiche de coûts'!J22</f>
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>739</v>
+      </c>
+      <c r="G22">
+        <f>G13/(G15-G10)</f>
+        <v>4.7184387290040135</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>740</v>
+      </c>
+      <c r="B27">
+        <f>'[1]Fiche de coûts'!$C$17</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>741</v>
+      </c>
+      <c r="B28" s="882">
+        <f>'Fiche de coûts'!$L$8</f>
+        <v>7871</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="883" t="s">
+        <v>742</v>
+      </c>
+      <c r="B29" s="884">
+        <f>'Fiche de coûts'!$L$9</f>
+        <v>6090.7380800000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="883" t="s">
+        <v>743</v>
+      </c>
+      <c r="B30" s="884">
+        <f>'Fiche de coûts'!$L$10</f>
+        <v>1780.2619199999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>620</v>
+      </c>
+      <c r="B31" s="882">
+        <f>'Fiche de coûts'!$J$22</f>
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>697</v>
+      </c>
+      <c r="B33">
+        <f>ROUNDUP(B29/(B31-B30/B27),0)</f>
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
@@ -17143,7 +18078,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
@@ -17951,7 +18886,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
@@ -17994,7 +18929,7 @@
       </c>
       <c r="C4" s="541"/>
       <c r="D4" s="26">
-        <f>B4*C4</f>
+        <f t="shared" ref="D4:D9" si="0">B4*C4</f>
         <v>0</v>
       </c>
     </row>
@@ -18007,7 +18942,7 @@
       </c>
       <c r="C5" s="541"/>
       <c r="D5" s="26">
-        <f t="shared" ref="D5:D8" si="0">B5*C5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -18057,27 +18992,27 @@
       <c r="B9" s="542"/>
       <c r="C9" s="541"/>
       <c r="D9" s="26">
-        <f>B9*C9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="844" t="s">
+      <c r="A10" s="854" t="s">
         <v>87</v>
       </c>
-      <c r="B10" s="844"/>
-      <c r="C10" s="844"/>
+      <c r="B10" s="854"/>
+      <c r="C10" s="854"/>
       <c r="D10" s="43">
         <f>SUM(D4:D9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="844" t="s">
+      <c r="A13" s="854" t="s">
         <v>88</v>
       </c>
-      <c r="B13" s="844"/>
-      <c r="C13" s="844"/>
+      <c r="B13" s="854"/>
+      <c r="C13" s="854"/>
       <c r="D13" s="43">
         <f>B18*C18+B19*C19+B20*C20+B21*C21+B22*C22+B23*C23+D18*E18+D19*E19+D20*E20+D21*E21+D22*E22+D23*E23+F18*G18+F19*G19+F20*G20+F21*G21+F22*G22+F23*G23+H18*I18+H19*I19+H20*I20+H21*I21+H22*I22+H23*I23+B29*C29+B30*C30+B31*C31+B32*C32+D29*E29+D30*E30+D31*E31+D32*E32+F29*G29+F30*G30+F31*G31+F32*G32+H29*I29+H30*I30+H31*I31+H32*I32+B37*C37+B38*C38+B39*C39+B40*C40+D37*E37+D38*E38+D39*E39+D40*E40+F37*G37+F38*G38+F39*G39+F40*G40+H37*I37+H38*I38+H39*I39+H40*I40+B45*C45+B46*C46+B47*C47+B48*C48+B49*C49+B50*C50+B51*C51+B52*C52+B54*C54+B55*C55+D45*E45+D46*E46+D47*E47+D48*E48+D49*E49+D50*E50+D51*E51+D52*E52+D54*E54+D55*E55+F45*G45+F46*G46+F47*G47+F48*G48+F49*G49+F50*G50+F51*G51+F52*G52+F53*G53+F54*G54+F55*G55+H45*I45+H46*I46+H47*I47+H48*I48+H49*I49+H50*I50+H51*I51+H52*I52+H53*I53+H54*I54+H55*I55+C59*D59+C61*D61+C63*D63+C65*D65+C66*D66+C67*D67+C68*D68+C69*D69+C70*D70+C73*D73+C74*D74+C75*D75+C76*D76+E59*F59+E61*F61+E63*F63+E65*F65+E66*F66+E67*F67+E68*F68+E69*F69+E70*F70++E73*F73+E74*F74+E75*F75+E76*F76</f>
         <v>400</v>
@@ -18085,42 +19020,42 @@
     </row>
     <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="1:9" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="841" t="s">
+      <c r="B15" s="851" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="842"/>
-      <c r="D15" s="842"/>
-      <c r="E15" s="843"/>
-      <c r="F15" s="841" t="s">
+      <c r="C15" s="852"/>
+      <c r="D15" s="852"/>
+      <c r="E15" s="853"/>
+      <c r="F15" s="851" t="s">
         <v>71</v>
       </c>
-      <c r="G15" s="842"/>
-      <c r="H15" s="842"/>
-      <c r="I15" s="843"/>
+      <c r="G15" s="852"/>
+      <c r="H15" s="852"/>
+      <c r="I15" s="853"/>
     </row>
     <row r="16" spans="1:9" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="845" t="s">
+      <c r="A16" s="855" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="826" t="s">
+      <c r="B16" s="836" t="s">
         <v>70</v>
       </c>
-      <c r="C16" s="827"/>
-      <c r="D16" s="840" t="s">
+      <c r="C16" s="837"/>
+      <c r="D16" s="850" t="s">
         <v>676</v>
       </c>
-      <c r="E16" s="829"/>
-      <c r="F16" s="826" t="s">
+      <c r="E16" s="839"/>
+      <c r="F16" s="836" t="s">
         <v>70</v>
       </c>
-      <c r="G16" s="839"/>
-      <c r="H16" s="840" t="s">
+      <c r="G16" s="849"/>
+      <c r="H16" s="850" t="s">
         <v>676</v>
       </c>
-      <c r="I16" s="829"/>
+      <c r="I16" s="839"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="846"/>
+      <c r="A17" s="856"/>
       <c r="B17" s="502" t="s">
         <v>161</v>
       </c>
@@ -18155,7 +19090,7 @@
       </c>
       <c r="C18" s="543"/>
       <c r="D18" s="516">
-        <f>ROUND(B18*0.7,0)</f>
+        <f t="shared" ref="D18:D23" si="1">ROUND(B18*0.7,0)</f>
         <v>259</v>
       </c>
       <c r="E18" s="543"/>
@@ -18164,7 +19099,7 @@
       </c>
       <c r="G18" s="537"/>
       <c r="H18" s="516">
-        <f>ROUND(F18*0.7,0)</f>
+        <f t="shared" ref="H18:H23" si="2">ROUND(F18*0.7,0)</f>
         <v>173</v>
       </c>
       <c r="I18" s="543"/>
@@ -18178,7 +19113,7 @@
       </c>
       <c r="C19" s="543"/>
       <c r="D19" s="516">
-        <f t="shared" ref="D19:D23" si="1">ROUND(B19*0.7,0)</f>
+        <f t="shared" si="1"/>
         <v>490</v>
       </c>
       <c r="E19" s="543"/>
@@ -18187,7 +19122,7 @@
       </c>
       <c r="G19" s="537"/>
       <c r="H19" s="516">
-        <f t="shared" ref="H19:H23" si="2">ROUND(F19*0.7,0)</f>
+        <f t="shared" si="2"/>
         <v>327</v>
       </c>
       <c r="I19" s="543"/>
@@ -18273,7 +19208,7 @@
       </c>
       <c r="E23" s="545"/>
       <c r="F23" s="518">
-        <f t="shared" ref="F23" si="3">ROUND(B23*0.65,0)</f>
+        <f>ROUND(B23*0.65,0)</f>
         <v>0</v>
       </c>
       <c r="G23" s="538"/>
@@ -18285,42 +19220,42 @@
     </row>
     <row r="25" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="26" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="841" t="s">
+      <c r="B26" s="851" t="s">
         <v>57</v>
       </c>
-      <c r="C26" s="842"/>
-      <c r="D26" s="842"/>
-      <c r="E26" s="843"/>
-      <c r="F26" s="842" t="s">
+      <c r="C26" s="852"/>
+      <c r="D26" s="852"/>
+      <c r="E26" s="853"/>
+      <c r="F26" s="852" t="s">
         <v>71</v>
       </c>
-      <c r="G26" s="842"/>
-      <c r="H26" s="842"/>
-      <c r="I26" s="843"/>
+      <c r="G26" s="852"/>
+      <c r="H26" s="852"/>
+      <c r="I26" s="853"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="847" t="s">
+      <c r="A27" s="857" t="s">
         <v>77</v>
       </c>
-      <c r="B27" s="826" t="s">
+      <c r="B27" s="836" t="s">
         <v>70</v>
       </c>
-      <c r="C27" s="827"/>
-      <c r="D27" s="828" t="s">
+      <c r="C27" s="837"/>
+      <c r="D27" s="838" t="s">
         <v>72</v>
       </c>
-      <c r="E27" s="829"/>
-      <c r="F27" s="826" t="s">
+      <c r="E27" s="839"/>
+      <c r="F27" s="836" t="s">
         <v>70</v>
       </c>
-      <c r="G27" s="827"/>
-      <c r="H27" s="828" t="s">
+      <c r="G27" s="837"/>
+      <c r="H27" s="838" t="s">
         <v>72</v>
       </c>
-      <c r="I27" s="829"/>
+      <c r="I27" s="839"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="848"/>
+      <c r="A28" s="858"/>
       <c r="B28" s="29" t="s">
         <v>161</v>
       </c>
@@ -18387,7 +19322,7 @@
       </c>
       <c r="G30" s="543"/>
       <c r="H30" s="519">
-        <f t="shared" ref="H30:H32" si="4">ROUND(F30*0.8,0)</f>
+        <f>ROUND(F30*0.8,0)</f>
         <v>280</v>
       </c>
       <c r="I30" s="543"/>
@@ -18410,7 +19345,7 @@
       </c>
       <c r="G31" s="543"/>
       <c r="H31" s="519">
-        <f t="shared" si="4"/>
+        <f>ROUND(F31*0.8,0)</f>
         <v>216</v>
       </c>
       <c r="I31" s="543"/>
@@ -18433,49 +19368,49 @@
       </c>
       <c r="G32" s="545"/>
       <c r="H32" s="520">
-        <f t="shared" si="4"/>
+        <f>ROUND(F32*0.8,0)</f>
         <v>232</v>
       </c>
       <c r="I32" s="545"/>
     </row>
     <row r="33" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="34" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="841" t="s">
+      <c r="B34" s="851" t="s">
         <v>57</v>
       </c>
-      <c r="C34" s="842"/>
-      <c r="D34" s="842"/>
-      <c r="E34" s="843"/>
-      <c r="F34" s="842" t="s">
+      <c r="C34" s="852"/>
+      <c r="D34" s="852"/>
+      <c r="E34" s="853"/>
+      <c r="F34" s="852" t="s">
         <v>71</v>
       </c>
-      <c r="G34" s="842"/>
-      <c r="H34" s="842"/>
-      <c r="I34" s="843"/>
+      <c r="G34" s="852"/>
+      <c r="H34" s="852"/>
+      <c r="I34" s="853"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="845" t="s">
+      <c r="A35" s="855" t="s">
         <v>69</v>
       </c>
-      <c r="B35" s="826" t="s">
+      <c r="B35" s="836" t="s">
         <v>70</v>
       </c>
-      <c r="C35" s="827"/>
-      <c r="D35" s="828" t="s">
+      <c r="C35" s="837"/>
+      <c r="D35" s="838" t="s">
         <v>72</v>
       </c>
-      <c r="E35" s="829"/>
-      <c r="F35" s="826" t="s">
+      <c r="E35" s="839"/>
+      <c r="F35" s="836" t="s">
         <v>70</v>
       </c>
-      <c r="G35" s="827"/>
-      <c r="H35" s="828" t="s">
+      <c r="G35" s="837"/>
+      <c r="H35" s="838" t="s">
         <v>72</v>
       </c>
-      <c r="I35" s="829"/>
+      <c r="I35" s="839"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="846"/>
+      <c r="A36" s="856"/>
       <c r="B36" s="29" t="s">
         <v>161</v>
       </c>
@@ -18542,7 +19477,7 @@
       </c>
       <c r="G38" s="543"/>
       <c r="H38" s="519">
-        <f t="shared" ref="H38:H40" si="5">ROUND(F38*0.8,0)</f>
+        <f>ROUND(F38*0.8,0)</f>
         <v>200</v>
       </c>
       <c r="I38" s="543"/>
@@ -18567,7 +19502,7 @@
       </c>
       <c r="G39" s="543"/>
       <c r="H39" s="519">
-        <f t="shared" si="5"/>
+        <f>ROUND(F39*0.8,0)</f>
         <v>200</v>
       </c>
       <c r="I39" s="543"/>
@@ -18590,49 +19525,49 @@
       </c>
       <c r="G40" s="545"/>
       <c r="H40" s="520">
-        <f t="shared" si="5"/>
+        <f>ROUND(F40*0.8,0)</f>
         <v>296</v>
       </c>
       <c r="I40" s="545"/>
     </row>
     <row r="41" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="42" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="832" t="s">
+      <c r="B42" s="842" t="s">
         <v>57</v>
       </c>
-      <c r="C42" s="833"/>
-      <c r="D42" s="833"/>
-      <c r="E42" s="834"/>
-      <c r="F42" s="835" t="s">
+      <c r="C42" s="843"/>
+      <c r="D42" s="843"/>
+      <c r="E42" s="844"/>
+      <c r="F42" s="845" t="s">
         <v>71</v>
       </c>
-      <c r="G42" s="833"/>
-      <c r="H42" s="833"/>
-      <c r="I42" s="836"/>
+      <c r="G42" s="843"/>
+      <c r="H42" s="843"/>
+      <c r="I42" s="846"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="845" t="s">
+      <c r="A43" s="855" t="s">
         <v>73</v>
       </c>
-      <c r="B43" s="826" t="s">
+      <c r="B43" s="836" t="s">
         <v>70</v>
       </c>
-      <c r="C43" s="827"/>
-      <c r="D43" s="828" t="s">
+      <c r="C43" s="837"/>
+      <c r="D43" s="838" t="s">
         <v>72</v>
       </c>
-      <c r="E43" s="829"/>
-      <c r="F43" s="826" t="s">
+      <c r="E43" s="839"/>
+      <c r="F43" s="836" t="s">
         <v>70</v>
       </c>
-      <c r="G43" s="827"/>
-      <c r="H43" s="828" t="s">
+      <c r="G43" s="837"/>
+      <c r="H43" s="838" t="s">
         <v>72</v>
       </c>
-      <c r="I43" s="829"/>
+      <c r="I43" s="839"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="846"/>
+      <c r="A44" s="856"/>
       <c r="B44" s="29" t="s">
         <v>161</v>
       </c>
@@ -18690,7 +19625,7 @@
       </c>
       <c r="C46" s="543"/>
       <c r="D46" s="519">
-        <f t="shared" ref="D46:D55" si="6">ROUND(B46*0.7,0)</f>
+        <f t="shared" ref="D46:D55" si="3">ROUND(B46*0.7,0)</f>
         <v>490</v>
       </c>
       <c r="E46" s="543"/>
@@ -18699,7 +19634,7 @@
       </c>
       <c r="G46" s="543"/>
       <c r="H46" s="519">
-        <f t="shared" ref="H46:H55" si="7">ROUND(F46*0.7,0)</f>
+        <f t="shared" ref="H46:H55" si="4">ROUND(F46*0.7,0)</f>
         <v>327</v>
       </c>
       <c r="I46" s="543"/>
@@ -18713,7 +19648,7 @@
       </c>
       <c r="C47" s="543"/>
       <c r="D47" s="519">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>770</v>
       </c>
       <c r="E47" s="543"/>
@@ -18722,7 +19657,7 @@
       </c>
       <c r="G47" s="543"/>
       <c r="H47" s="519">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>513</v>
       </c>
       <c r="I47" s="543"/>
@@ -18736,7 +19671,7 @@
       </c>
       <c r="C48" s="543"/>
       <c r="D48" s="519">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>1190</v>
       </c>
       <c r="E48" s="543"/>
@@ -18745,7 +19680,7 @@
       </c>
       <c r="G48" s="543"/>
       <c r="H48" s="519">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>793</v>
       </c>
       <c r="I48" s="543"/>
@@ -18759,7 +19694,7 @@
       </c>
       <c r="C49" s="543"/>
       <c r="D49" s="519">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>420</v>
       </c>
       <c r="E49" s="543"/>
@@ -18768,7 +19703,7 @@
       </c>
       <c r="G49" s="543"/>
       <c r="H49" s="519">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>280</v>
       </c>
       <c r="I49" s="543"/>
@@ -18782,7 +19717,7 @@
       </c>
       <c r="C50" s="543"/>
       <c r="D50" s="519">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>560</v>
       </c>
       <c r="E50" s="543"/>
@@ -18791,7 +19726,7 @@
       </c>
       <c r="G50" s="543"/>
       <c r="H50" s="519">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>373</v>
       </c>
       <c r="I50" s="543"/>
@@ -18805,7 +19740,7 @@
       </c>
       <c r="C51" s="543"/>
       <c r="D51" s="519">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>840</v>
       </c>
       <c r="E51" s="543"/>
@@ -18814,7 +19749,7 @@
       </c>
       <c r="G51" s="543"/>
       <c r="H51" s="519">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>560</v>
       </c>
       <c r="I51" s="543"/>
@@ -18826,14 +19761,14 @@
       <c r="B52" s="223"/>
       <c r="C52" s="224"/>
       <c r="D52" s="225">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E52" s="224"/>
       <c r="F52" s="223"/>
       <c r="G52" s="224"/>
       <c r="H52" s="225">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I52" s="224"/>
@@ -18865,7 +19800,7 @@
       </c>
       <c r="C54" s="543"/>
       <c r="D54" s="519">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>1680</v>
       </c>
       <c r="E54" s="543"/>
@@ -18874,7 +19809,7 @@
       </c>
       <c r="G54" s="543"/>
       <c r="H54" s="519">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>1120</v>
       </c>
       <c r="I54" s="543"/>
@@ -18888,7 +19823,7 @@
       </c>
       <c r="C55" s="545"/>
       <c r="D55" s="520">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>245</v>
       </c>
       <c r="E55" s="545"/>
@@ -18897,31 +19832,31 @@
       </c>
       <c r="G55" s="545"/>
       <c r="H55" s="520">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>163</v>
       </c>
       <c r="I55" s="545"/>
     </row>
     <row r="56" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="57" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="830" t="s">
+      <c r="A57" s="840" t="s">
         <v>74</v>
       </c>
-      <c r="B57" s="837" t="s">
+      <c r="B57" s="847" t="s">
         <v>1</v>
       </c>
-      <c r="C57" s="826" t="s">
+      <c r="C57" s="836" t="s">
         <v>70</v>
       </c>
-      <c r="D57" s="827"/>
-      <c r="E57" s="828" t="s">
+      <c r="D57" s="837"/>
+      <c r="E57" s="838" t="s">
         <v>72</v>
       </c>
-      <c r="F57" s="829"/>
+      <c r="F57" s="839"/>
     </row>
     <row r="58" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="831"/>
-      <c r="B58" s="838"/>
+      <c r="A58" s="841"/>
+      <c r="B58" s="848"/>
       <c r="C58" s="40" t="s">
         <v>161</v>
       </c>
@@ -19005,7 +19940,7 @@
       </c>
       <c r="D63" s="543"/>
       <c r="E63" s="265">
-        <f t="shared" ref="E63:E74" si="8">ROUND(C63*0.7,0)</f>
+        <f t="shared" ref="E63:E74" si="5">ROUND(C63*0.7,0)</f>
         <v>70</v>
       </c>
       <c r="F63" s="543"/>
@@ -19022,7 +19957,7 @@
       </c>
       <c r="D64" s="543"/>
       <c r="E64" s="265">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>84</v>
       </c>
       <c r="F64" s="543"/>
@@ -19039,7 +19974,7 @@
       </c>
       <c r="D65" s="543"/>
       <c r="E65" s="265">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>350</v>
       </c>
       <c r="F65" s="543"/>
@@ -19056,7 +19991,7 @@
       </c>
       <c r="D66" s="543"/>
       <c r="E66" s="265">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>560</v>
       </c>
       <c r="F66" s="543"/>
@@ -19073,7 +20008,7 @@
       </c>
       <c r="D67" s="543"/>
       <c r="E67" s="265">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>84</v>
       </c>
       <c r="F67" s="543"/>
@@ -19090,7 +20025,7 @@
       </c>
       <c r="D68" s="543"/>
       <c r="E68" s="265">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>140</v>
       </c>
       <c r="F68" s="543"/>
@@ -19107,7 +20042,7 @@
       </c>
       <c r="D69" s="543"/>
       <c r="E69" s="265">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>210</v>
       </c>
       <c r="F69" s="543"/>
@@ -19124,7 +20059,7 @@
       </c>
       <c r="D70" s="543"/>
       <c r="E70" s="265">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>70</v>
       </c>
       <c r="F70" s="543"/>
@@ -19141,7 +20076,7 @@
       </c>
       <c r="D71" s="544"/>
       <c r="E71" s="265">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>105</v>
       </c>
       <c r="F71" s="544"/>
@@ -19170,7 +20105,7 @@
       </c>
       <c r="D73" s="544"/>
       <c r="E73" s="265">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>210</v>
       </c>
       <c r="F73" s="544"/>
@@ -19187,7 +20122,7 @@
       </c>
       <c r="D74" s="544"/>
       <c r="E74" s="265">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>315</v>
       </c>
       <c r="F74" s="544"/>
@@ -19279,7 +20214,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
@@ -19329,7 +20264,7 @@
         <v>8</v>
       </c>
       <c r="E4" s="491">
-        <f>B4*D4*C4</f>
+        <f t="shared" ref="E4:E9" si="0">B4*D4*C4</f>
         <v>0</v>
       </c>
     </row>
@@ -19348,7 +20283,7 @@
         <v>8</v>
       </c>
       <c r="E5" s="491">
-        <f t="shared" ref="E5:E9" si="0">B5*D5*C5</f>
+        <f t="shared" si="0"/>
         <v>294.71999999999997</v>
       </c>
     </row>
@@ -19399,7 +20334,7 @@
         <v>6</v>
       </c>
       <c r="E8" s="491">
-        <f t="shared" ref="E8" si="1">B8*D8*C8</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -19419,25 +20354,25 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="849" t="s">
+      <c r="A10" s="859" t="s">
         <v>92</v>
       </c>
-      <c r="B10" s="850"/>
-      <c r="C10" s="850"/>
-      <c r="D10" s="850"/>
+      <c r="B10" s="860"/>
+      <c r="C10" s="860"/>
+      <c r="D10" s="860"/>
       <c r="E10" s="492">
         <f>SUM(E4:E9)</f>
         <v>337.55999999999995</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="851" t="s">
+      <c r="A11" s="861" t="s">
         <v>352</v>
       </c>
-      <c r="B11" s="852"/>
-      <c r="C11" s="852"/>
-      <c r="D11" s="852"/>
-      <c r="E11" s="853"/>
+      <c r="B11" s="862"/>
+      <c r="C11" s="862"/>
+      <c r="D11" s="862"/>
+      <c r="E11" s="863"/>
     </row>
     <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:5" ht="60" x14ac:dyDescent="0.25">
@@ -19470,7 +20405,7 @@
         <v>6</v>
       </c>
       <c r="E14" s="494">
-        <f>B14*D14*C14</f>
+        <f t="shared" ref="E14:E21" si="1">B14*D14*C14</f>
         <v>0</v>
       </c>
     </row>
@@ -19489,7 +20424,7 @@
         <v>6</v>
       </c>
       <c r="E15" s="494">
-        <f>B15*D15*C15</f>
+        <f t="shared" si="1"/>
         <v>187.5</v>
       </c>
     </row>
@@ -19506,7 +20441,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="494">
-        <f t="shared" ref="E16:E17" si="2">B16*D16*C16</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -19521,7 +20456,7 @@
         <v>6</v>
       </c>
       <c r="E17" s="494">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -19529,10 +20464,10 @@
       <c r="A18" s="605" t="s">
         <v>712</v>
       </c>
-      <c r="B18" s="874">
+      <c r="B18" s="643">
         <v>200</v>
       </c>
-      <c r="C18" s="875">
+      <c r="C18" s="644">
         <v>1</v>
       </c>
       <c r="D18" s="493">
@@ -19540,7 +20475,7 @@
         <v>6</v>
       </c>
       <c r="E18" s="494">
-        <f t="shared" ref="E18:E20" si="3">B18*D18*C18</f>
+        <f t="shared" si="1"/>
         <v>1200</v>
       </c>
       <c r="F18" s="177"/>
@@ -19556,7 +20491,7 @@
         <v>6</v>
       </c>
       <c r="E19" s="494">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F19" s="177"/>
@@ -19572,7 +20507,7 @@
         <v>6</v>
       </c>
       <c r="E20" s="494">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F20" s="177"/>
@@ -19588,7 +20523,7 @@
         <v>6</v>
       </c>
       <c r="E21" s="496">
-        <f>B21*D21*C21</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F21" s="177"/>
@@ -19602,527 +20537,6 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <sheetPr>
-    <tabColor theme="8" tint="0.59999389629810485"/>
-  </sheetPr>
-  <dimension ref="A1:J48"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="35.85546875" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" customWidth="1"/>
-    <col min="9" max="9" width="16.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="65" t="s">
-        <v>110</v>
-      </c>
-      <c r="B2" s="65"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="65"/>
-      <c r="B3" s="65"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="65"/>
-      <c r="B4" s="65"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="65"/>
-      <c r="B5" s="65"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="65"/>
-      <c r="B6" s="65"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="65"/>
-      <c r="B7" s="65"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="65"/>
-      <c r="B8" s="65"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="65"/>
-      <c r="B9" s="65"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="65"/>
-      <c r="B10" s="65"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="65"/>
-      <c r="B11" s="65"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="65"/>
-      <c r="B12" s="65"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="65"/>
-      <c r="B13" s="65"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="65"/>
-      <c r="B14" s="65"/>
-    </row>
-    <row r="15" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:9" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="864" t="s">
-        <v>112</v>
-      </c>
-      <c r="D16" s="865"/>
-      <c r="E16" s="864" t="s">
-        <v>111</v>
-      </c>
-      <c r="F16" s="866"/>
-      <c r="G16" s="864" t="s">
-        <v>141</v>
-      </c>
-      <c r="H16" s="866"/>
-      <c r="I16" s="862" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="67" t="s">
-        <v>113</v>
-      </c>
-      <c r="B17" s="68" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="72" t="s">
-        <v>257</v>
-      </c>
-      <c r="D17" s="73" t="s">
-        <v>85</v>
-      </c>
-      <c r="E17" s="72" t="s">
-        <v>257</v>
-      </c>
-      <c r="F17" s="73" t="s">
-        <v>85</v>
-      </c>
-      <c r="G17" s="72" t="s">
-        <v>257</v>
-      </c>
-      <c r="H17" s="73" t="s">
-        <v>85</v>
-      </c>
-      <c r="I17" s="863"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="66" t="s">
-        <v>103</v>
-      </c>
-      <c r="B18" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="C18" s="616"/>
-      <c r="D18" s="536"/>
-      <c r="E18" s="616"/>
-      <c r="F18" s="536"/>
-      <c r="G18" s="616"/>
-      <c r="H18" s="536"/>
-      <c r="I18" s="71">
-        <f>C18*D18+E18*F18+G18*H18</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="588" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="66" t="s">
-        <v>349</v>
-      </c>
-      <c r="B19" s="36" t="s">
-        <v>108</v>
-      </c>
-      <c r="C19" s="539"/>
-      <c r="D19" s="536"/>
-      <c r="E19" s="539"/>
-      <c r="F19" s="536"/>
-      <c r="G19" s="539"/>
-      <c r="H19" s="536"/>
-      <c r="I19" s="69">
-        <f t="shared" ref="I19:I21" si="0">C19*D19+E19*F19+G19*H19</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="66" t="s">
-        <v>350</v>
-      </c>
-      <c r="B20" s="36" t="s">
-        <v>108</v>
-      </c>
-      <c r="C20" s="539"/>
-      <c r="D20" s="536"/>
-      <c r="E20" s="539"/>
-      <c r="F20" s="536"/>
-      <c r="G20" s="539"/>
-      <c r="H20" s="536"/>
-      <c r="I20" s="69">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="66" t="s">
-        <v>351</v>
-      </c>
-      <c r="B21" s="36" t="s">
-        <v>108</v>
-      </c>
-      <c r="C21" s="539"/>
-      <c r="D21" s="536"/>
-      <c r="E21" s="539"/>
-      <c r="F21" s="536"/>
-      <c r="G21" s="539"/>
-      <c r="H21" s="536"/>
-      <c r="I21" s="69">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="B22" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="C22" s="614">
-        <v>130</v>
-      </c>
-      <c r="D22" s="615"/>
-      <c r="E22" s="614">
-        <v>110</v>
-      </c>
-      <c r="F22" s="537"/>
-      <c r="G22" s="539"/>
-      <c r="H22" s="537"/>
-      <c r="I22" s="69">
-        <f t="shared" ref="I22:I25" si="1">C22*D22+E22*F22+G22*H22</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="B23" s="36" t="s">
-        <v>108</v>
-      </c>
-      <c r="C23" s="614">
-        <v>22</v>
-      </c>
-      <c r="D23" s="615"/>
-      <c r="E23" s="614">
-        <v>22</v>
-      </c>
-      <c r="F23" s="537"/>
-      <c r="G23" s="539"/>
-      <c r="H23" s="537"/>
-      <c r="I23" s="69">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="B24" s="36" t="s">
-        <v>108</v>
-      </c>
-      <c r="C24" s="614">
-        <v>20.2</v>
-      </c>
-      <c r="D24" s="615"/>
-      <c r="E24" s="614">
-        <v>20.2</v>
-      </c>
-      <c r="F24" s="537"/>
-      <c r="G24" s="539"/>
-      <c r="H24" s="537"/>
-      <c r="I24" s="69">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="631" t="s">
-        <v>700</v>
-      </c>
-      <c r="B25" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="C25" s="612"/>
-      <c r="D25" s="538"/>
-      <c r="E25" s="612"/>
-      <c r="F25" s="538"/>
-      <c r="G25" s="612"/>
-      <c r="H25" s="538"/>
-      <c r="I25" s="70">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="I26" s="74">
-        <f>SUM(I18:I25)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="I27" s="375"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="65" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="266" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="37" spans="1:9" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="B37" s="869" t="s">
-        <v>573</v>
-      </c>
-      <c r="C37" s="870"/>
-      <c r="D37" s="870"/>
-      <c r="E37" s="870"/>
-      <c r="F37" s="870"/>
-      <c r="G37" s="870"/>
-      <c r="H37" s="871"/>
-      <c r="I37" s="591"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="467"/>
-      <c r="B38" s="592"/>
-      <c r="C38" s="467"/>
-      <c r="D38" s="467"/>
-      <c r="E38" s="467"/>
-      <c r="F38" s="467"/>
-      <c r="G38" s="467"/>
-      <c r="H38" s="593"/>
-      <c r="I38" s="467"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="467"/>
-      <c r="B39" s="854" t="s">
-        <v>562</v>
-      </c>
-      <c r="C39" s="855"/>
-      <c r="D39" s="477"/>
-      <c r="E39" s="468"/>
-      <c r="F39" s="469"/>
-      <c r="G39" s="469"/>
-      <c r="H39" s="594"/>
-      <c r="I39" s="467"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="467"/>
-      <c r="B40" s="592"/>
-      <c r="C40" s="467"/>
-      <c r="D40" s="467"/>
-      <c r="E40" s="467"/>
-      <c r="F40" s="467"/>
-      <c r="G40" s="467"/>
-      <c r="H40" s="593"/>
-      <c r="I40" s="467"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="467"/>
-      <c r="B41" s="595"/>
-      <c r="C41" s="470"/>
-      <c r="D41" s="856" t="s">
-        <v>563</v>
-      </c>
-      <c r="E41" s="856"/>
-      <c r="F41" s="856"/>
-      <c r="G41" s="856"/>
-      <c r="H41" s="857"/>
-      <c r="I41" s="467"/>
-    </row>
-    <row r="42" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A42" s="589"/>
-      <c r="B42" s="858" t="s">
-        <v>564</v>
-      </c>
-      <c r="C42" s="859"/>
-      <c r="D42" s="471" t="s">
-        <v>565</v>
-      </c>
-      <c r="E42" s="587" t="s">
-        <v>566</v>
-      </c>
-      <c r="F42" s="471" t="s">
-        <v>567</v>
-      </c>
-      <c r="G42" s="587" t="s">
-        <v>568</v>
-      </c>
-      <c r="H42" s="596" t="s">
-        <v>569</v>
-      </c>
-      <c r="I42" s="589"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="467"/>
-      <c r="B43" s="867" t="s">
-        <v>570</v>
-      </c>
-      <c r="C43" s="868"/>
-      <c r="D43" s="473">
-        <v>0.32</v>
-      </c>
-      <c r="E43" s="473">
-        <v>0.35</v>
-      </c>
-      <c r="F43" s="473">
-        <v>0.37</v>
-      </c>
-      <c r="G43" s="473">
-        <v>0.08</v>
-      </c>
-      <c r="H43" s="597">
-        <v>0.12</v>
-      </c>
-      <c r="I43" s="467"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="467"/>
-      <c r="B44" s="598" t="s">
-        <v>571</v>
-      </c>
-      <c r="C44" s="472"/>
-      <c r="D44" s="473">
-        <v>0.15</v>
-      </c>
-      <c r="E44" s="473">
-        <v>0.17</v>
-      </c>
-      <c r="F44" s="473">
-        <v>0.18</v>
-      </c>
-      <c r="G44" s="473">
-        <v>0.08</v>
-      </c>
-      <c r="H44" s="597">
-        <v>0.12</v>
-      </c>
-      <c r="I44" s="467"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="467"/>
-      <c r="B45" s="595"/>
-      <c r="C45" s="470"/>
-      <c r="D45" s="470"/>
-      <c r="E45" s="470"/>
-      <c r="F45" s="470"/>
-      <c r="G45" s="470"/>
-      <c r="H45" s="599"/>
-      <c r="I45" s="467"/>
-    </row>
-    <row r="46" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A46" s="467"/>
-      <c r="B46" s="595"/>
-      <c r="C46" s="470"/>
-      <c r="D46" s="474" t="s">
-        <v>565</v>
-      </c>
-      <c r="E46" s="475" t="s">
-        <v>566</v>
-      </c>
-      <c r="F46" s="474" t="s">
-        <v>567</v>
-      </c>
-      <c r="G46" s="587" t="s">
-        <v>568</v>
-      </c>
-      <c r="H46" s="600" t="s">
-        <v>569</v>
-      </c>
-      <c r="I46" s="467"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="590"/>
-      <c r="B47" s="860" t="s">
-        <v>572</v>
-      </c>
-      <c r="C47" s="861"/>
-      <c r="D47" s="476">
-        <f>IF(D39&lt;1000,(D39*D43),(D39*D44))</f>
-        <v>0</v>
-      </c>
-      <c r="E47" s="476">
-        <f>IF(D39&lt;1000,(D39*E43),(D39*E44))</f>
-        <v>0</v>
-      </c>
-      <c r="F47" s="476">
-        <f>IF(D39&lt;1000,(D39*F43),(D39*F44))</f>
-        <v>0</v>
-      </c>
-      <c r="G47" s="476">
-        <f>IF(D39&lt;1000,(D39*G43),(D39*G44))</f>
-        <v>0</v>
-      </c>
-      <c r="H47" s="601">
-        <f>IF(D39&lt;1000,(D39*H43),(D39*H44))</f>
-        <v>0</v>
-      </c>
-      <c r="I47" s="590"/>
-    </row>
-    <row r="48" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="467"/>
-      <c r="B48" s="602"/>
-      <c r="C48" s="603"/>
-      <c r="D48" s="603"/>
-      <c r="E48" s="603"/>
-      <c r="F48" s="603"/>
-      <c r="G48" s="603"/>
-      <c r="H48" s="604"/>
-      <c r="I48" s="467"/>
-    </row>
-  </sheetData>
-  <sheetProtection sheet="1" scenarios="1"/>
-  <mergeCells count="10">
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B37:H37"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="A30" r:id="rId1" xr:uid="{00000000-0004-0000-0800-000000000000}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId2"/>
-  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
